--- a/rileo_data_enrichment.xlsx
+++ b/rileo_data_enrichment.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D147"/>
+  <dimension ref="A1:D149"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="54.63" customWidth="1" style="15" min="1" max="1"/>
@@ -1259,7 +1259,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>/cancel my subscription to ruut/i,</t>
+          <t>/cancel my subscription to rileo/i,</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>/cancel my account/i,</t>
+          <t>/mobility program add-on/i,</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>/cancel my ruut subscription/i,</t>
+          <t>/cancel my rileo subscription/i,</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -1463,10 +1463,14 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>/cancel all subscriptions to ruut/i,</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="n"/>
+          <t>/cancel all subscriptions to rileo/i,</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>/reimburst/i,</t>
+        </is>
+      </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
           <t>/Mobility Program/i,</t>
@@ -1491,11 +1495,6 @@
           <t>/end my subscription/i,</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>/mobility program add-on/i,</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -1633,7 +1632,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>/cancel my subscription for ruut/i,</t>
+          <t>/cancel my subscription for rileo/i,</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1646,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>/cancel my ruut subscription/i,</t>
+          <t>/cancel my rileo subscription/i,</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1702,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>/ruut account has been canceled/i,</t>
+          <t>/rileo account has been canceled/i,</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1800,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>/cancel my subscription with ruut/i,</t>
+          <t>/cancel my subscription with rileo/i,</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1835,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>/cancel ruut/i,</t>
+          <t>/cancel rileo/i,</t>
         </is>
       </c>
     </row>
@@ -1885,14 +1884,14 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>/cancel ruut subscription/i,</t>
+          <t>/cancel rileo subscription/i,</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>/cancel my subscription with ruut/i,</t>
+          <t>/cancel my subscription with rileo/i,</t>
         </is>
       </c>
     </row>
@@ -2110,6 +2109,20 @@
       <c r="A147" s="3" t="inlineStr">
         <is>
           <t>/stop my payments/i,</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>/dar de baja (a la )?aplicación/i,</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>/cancel my account/i,</t>
         </is>
       </c>
     </row>

--- a/rileo_data_enrichment.xlsx
+++ b/rileo_data_enrichment.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D149"/>
+  <dimension ref="A1:D151"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="54.63" customWidth="1" style="15" min="1" max="1"/>
@@ -1495,6 +1495,11 @@
           <t>/end my subscription/i,</t>
         </is>
       </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>/deletion/i,</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -2123,6 +2128,20 @@
       <c r="A149" s="4" t="inlineStr">
         <is>
           <t>/cancel my account/i,</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>/annulé mon abonnement/,i</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>/quiero darme de baja/,i</t>
         </is>
       </c>
     </row>

--- a/rileo_data_enrichment.xlsx
+++ b/rileo_data_enrichment.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="561">
   <si>
     <t>Cancel</t>
   </si>
@@ -831,258 +831,285 @@
     <t xml:space="preserve">/annulé mon abonnement/i, </t>
   </si>
   <si>
-    <t>/quiero darme de baja/i,</t>
-  </si>
-  <si>
-    <t>&gt; darme de baja</t>
+    <t>/darme de baja/i,</t>
+  </si>
+  <si>
+    <t>/résilier (la période d')?essai/i,</t>
   </si>
   <si>
     <t>/résilier (.*)?abonnement/i,</t>
   </si>
   <si>
+    <t>/vorrei (togliere|cancellare|annullare|eliminare|disdire) (l')?abbonamento/i,</t>
+  </si>
+  <si>
+    <t>/voglio (togliere|cancellare|annullare|eliminare|disdire) (l')?abbonamento/i,</t>
+  </si>
+  <si>
+    <t>/togliere (l')?abbonamento/i,</t>
+  </si>
+  <si>
+    <t>/disdire (l')?abbonamento/i,</t>
+  </si>
+  <si>
+    <t>/eliminare (l')?abbonamento/i,</t>
+  </si>
+  <si>
+    <t>/rimuovere (l')?abbonamento/i,</t>
+  </si>
+  <si>
+    <t>/disattivare (l')?abbonamento/i,</t>
+  </si>
+  <si>
+    <t>/recedere (dal|dall')?abbonamento/i,</t>
+  </si>
+  <si>
+    <t>/non voglio (più )?(l')?abbonamento/i,</t>
+  </si>
+  <si>
+    <t>/返金/i,</t>
+  </si>
+  <si>
+    <t>/詐欺として報告/i,</t>
+  </si>
+  <si>
+    <t>/(動作しない|機能しない)/i,</t>
+  </si>
+  <si>
     <t>|継続課金)を(やめる|停止|解除)/i,</t>
   </si>
   <si>
-    <t>/返金/i,</t>
-  </si>
-  <si>
-    <t>/詐欺として報告/i,</t>
-  </si>
-  <si>
-    <t>/(動作しない|機能しない)/i,</t>
+    <t>/請求を返して/i,</t>
+  </si>
+  <si>
+    <t>/(異議申し立て|チャージバック)をする/i,</t>
+  </si>
+  <si>
+    <t>/受け取っていない/i,</t>
   </si>
   <si>
     <t>/(メンバーシップ|支払い|自動支払い|請求|引き落とし|自動更新)を?(止める|停止)/i,</t>
   </si>
   <si>
-    <t>/請求を返して/i,</t>
-  </si>
-  <si>
-    <t>/(異議申し立て|チャージバック)をする/i,</t>
-  </si>
-  <si>
-    <t>/受け取っていない/i,</t>
+    <t>/支払いを返して/i,</t>
+  </si>
+  <si>
+    <t>/(銀行|クレジットカード|カード発行会社|金融機関)に連絡して返金/i,</t>
   </si>
   <si>
     <t>/(サービス|サブスクリプション|メンバーシップ)を続けたくない/i,</t>
   </si>
   <si>
-    <t>/支払いを返して/i,</t>
-  </si>
-  <si>
-    <t>/(銀行|クレジットカード|カード発行会社|金融機関)に連絡して返金/i,</t>
+    <t>/お金を返して/i,</t>
+  </si>
+  <si>
+    <t>/自分で銀行を通じて返金/i,</t>
+  </si>
+  <si>
+    <t>/クラッシュする/i,</t>
   </si>
   <si>
     <t>/サブスクリプションは(必要ない|要らない)/i,</t>
   </si>
   <si>
-    <t>/お金を返して/i,</t>
-  </si>
-  <si>
-    <t>/自分で銀行を通じて返金/i,</t>
-  </si>
-  <si>
-    <t>/クラッシュする/i,</t>
+    <t>/取り消し/i,</t>
+  </si>
+  <si>
+    <t>/請求を(取り消し|差し戻し)/i,</t>
+  </si>
+  <si>
+    <t>/品質が悪い/i,</t>
   </si>
   <si>
     <t>/サブスクリプションに(興味がない|興味はない)/i,</t>
   </si>
   <si>
-    <t>/取り消し/i,</t>
-  </si>
-  <si>
-    <t>/請求を(取り消し|差し戻し)/i,</t>
-  </si>
-  <si>
-    <t>/品質が悪い/i,</t>
+    <t>/返済/i,</t>
+  </si>
+  <si>
+    <t>/PayPalに連絡して返金/i,</t>
+  </si>
+  <si>
+    <t>/品質が低い/i,</t>
   </si>
   <si>
     <t>/(サブスクリプション|メンバーシップ)の解約を希望/i,</t>
   </si>
   <si>
-    <t>/返済/i,</t>
-  </si>
-  <si>
-    <t>/PayPalに連絡して返金/i,</t>
-  </si>
-  <si>
-    <t>/品質が低い/i,</t>
+    <t>/返金して/i,</t>
+  </si>
+  <si>
+    <t>/PayPalの買い手保護を申請/i,</t>
+  </si>
+  <si>
+    <t>/使えない/i,</t>
   </si>
   <si>
     <t>/(サブスクリプション|メンバーシップ)が解約されたことを確認/i,</t>
   </si>
   <si>
-    <t>/返金して/i,</t>
-  </si>
-  <si>
-    <t>/PayPalの買い手保護を申請/i,</t>
-  </si>
-  <si>
-    <t>/使えない/i,</t>
+    <t>/払い戻して(ほしい)?/i,</t>
+  </si>
+  <si>
+    <t>/(Google Play|App Store)に報告/i,</t>
+  </si>
+  <si>
+    <t>/報告します/i,</t>
   </si>
   <si>
     <t>/(サブスクリプション|メンバーシップ|アカウント)を無効化/i,</t>
   </si>
   <si>
-    <t>/払い戻して(ほしい)?/i,</t>
-  </si>
-  <si>
-    <t>/(Google Play|App Store)に報告/i,</t>
-  </si>
-  <si>
-    <t>/報告します/i,</t>
+    <t>/返金して(ほしい)?/i,</t>
+  </si>
+  <si>
+    <t>/銀行が詐欺と(判断|通知)した/i,</t>
+  </si>
+  <si>
+    <t>/投稿します/i,</t>
   </si>
   <si>
     <t>/(.*)(サブスクリプション|メンバーシップ|アカウント|更新)を(解約|キャンセル)/i,</t>
   </si>
   <si>
-    <t>/返金して(ほしい)?/i,</t>
-  </si>
-  <si>
-    <t>/銀行が詐欺と(判断|通知)した/i,</t>
-  </si>
-  <si>
-    <t>/投稿します/i,</t>
+    <t>/異議申し立て中/i,</t>
   </si>
   <si>
     <t>/(サブスクリプション|メンバーシップ|アカウント|更新)を停止/i,</t>
   </si>
   <si>
-    <t>/異議申し立て中/i,</t>
+    <t>/異議申し立て/i,</t>
+  </si>
+  <si>
+    <t>/変換できない/i,</t>
   </si>
   <si>
     <t>/(サブスクリプション|メンバーシップ|更新)を削除/i,</t>
   </si>
   <si>
-    <t>/異議申し立て/i,</t>
-  </si>
-  <si>
-    <t>/変換できない/i,</t>
+    <t>/注文していない/i,</t>
+  </si>
+  <si>
+    <t>/異議申し立て済み/i,</t>
+  </si>
+  <si>
+    <t>/変換できなかった/i,</t>
   </si>
   <si>
     <t>/(配信停止|購読解除)/i,</t>
   </si>
   <si>
-    <t>/注文していない/i,</t>
-  </si>
-  <si>
-    <t>/異議申し立て済み/i,</t>
-  </si>
-  <si>
-    <t>/変換できなかった/i,</t>
+    <t>/(注文|支払い)をキャンセル/i,</t>
+  </si>
+  <si>
+    <t>/ふざけるな/i,</t>
   </si>
   <si>
     <t>/(解約|キャンセル)/i,</t>
   </si>
   <si>
-    <t>/(注文|支払い)をキャンセル/i,</t>
-  </si>
-  <si>
-    <t>/ふざけるな/i,</t>
+    <t>/支払いの取り消し/i,</t>
+  </si>
+  <si>
+    <t>/クソ/i,</t>
   </si>
   <si>
     <t>/(サブスクリプション|メンバーシップ)を終了/i,</t>
   </si>
   <si>
-    <t>/支払いの取り消し/i,</t>
-  </si>
-  <si>
-    <t>/クソ/i,</t>
+    <t>/ばかげている/i,</t>
+  </si>
+  <si>
+    <t>/問題/i,</t>
   </si>
   <si>
     <t>/(サブスクリプション|メンバーシップ)を終わらせる/i,</t>
   </si>
   <si>
-    <t>/ばかげている/i,</t>
-  </si>
-  <si>
-    <t>/問題/i,</t>
+    <t>/払い戻し/i,</t>
   </si>
   <si>
     <t>/やめたい/i,</t>
   </si>
   <si>
-    <t>/払い戻し/i,</t>
+    <t>/払い戻し済み/i,</t>
+  </si>
+  <si>
+    <t>/エラー/i,</t>
   </si>
   <si>
     <t>/(解約|解除)/i,</t>
   </si>
   <si>
-    <t>/払い戻し済み/i,</t>
-  </si>
-  <si>
-    <t>/エラー/i,</t>
-  </si>
-  <si>
     <t>/解約する/i,</t>
   </si>
   <si>
+    <t>/削除/i,</t>
+  </si>
+  <si>
     <t>/(取り消す|撤回)/i,</t>
   </si>
   <si>
-    <t>/削除/i,</t>
+    <t>/取り消された/i,</t>
+  </si>
+  <si>
+    <t>/データ削除/i,</t>
   </si>
   <si>
     <t>/サブスクリプションを(解約|終了)/i,</t>
   </si>
   <si>
-    <t>/取り消された/i,</t>
-  </si>
-  <si>
-    <t>/データ削除/i,</t>
+    <t>/個人データ/i,</t>
   </si>
   <si>
     <t>/サブスクリプションを取り消す/i,</t>
   </si>
   <si>
-    <t>/個人データ/i,</t>
+    <t>/取引/i,</t>
+  </si>
+  <si>
+    <t>/請求書/i,</t>
   </si>
   <si>
     <t>/サブスクリプションの停止/i,</t>
   </si>
   <si>
-    <t>/取引/i,</t>
-  </si>
-  <si>
-    <t>/請求書/i,</t>
+    <t>/(引き落とし|出金)/i,</t>
+  </si>
+  <si>
+    <t>/請求/i,</t>
   </si>
   <si>
     <t>/解約/i,</t>
   </si>
   <si>
-    <t>/(引き落とし|出金)/i,</t>
-  </si>
-  <si>
-    <t>/請求/i,</t>
+    <t>/支払った/i,</t>
+  </si>
+  <si>
+    <t>/電子請求書/i,</t>
   </si>
   <si>
     <t>/解約通知/i,</t>
   </si>
   <si>
-    <t>/支払った/i,</t>
-  </si>
-  <si>
-    <t>/電子請求書/i,</t>
+    <t>/領収書/i,</t>
+  </si>
+  <si>
+    <t>/請求(?!期間)/i,</t>
   </si>
   <si>
     <t>/キャンセルする/i,</t>
   </si>
   <si>
-    <t>/領収書/i,</t>
-  </si>
-  <si>
-    <t>/請求(?!期間)/i,</t>
-  </si>
-  <si>
     <t>/中断する/i,</t>
   </si>
   <si>
+    <t>/請求(?!\s*期間)/i,</t>
+  </si>
+  <si>
     <t>/停止する/i,</t>
   </si>
   <si>
-    <t>/請求(?!\s*期間)/i,</t>
-  </si>
-  <si>
     <t>/サブスクリプションを解約/i,</t>
   </si>
   <si>
@@ -1092,138 +1119,138 @@
     <t>/アップロード失敗/i,</t>
   </si>
   <si>
+    <t>/資金を返して/i,</t>
+  </si>
+  <si>
+    <t>/アカウントの削除/i,</t>
+  </si>
+  <si>
     <t>/キャンセル/i,</t>
   </si>
   <si>
-    <t>/資金を返して/i,</t>
-  </si>
-  <si>
-    <t>/アカウントの削除/i,</t>
-  </si>
-  <si>
     <t>/そのサブスクリプションを解約/i,</t>
   </si>
   <si>
+    <t>/アカウント削除/i,</t>
+  </si>
+  <si>
     <t>/サブスクリプションの解約/i,</t>
   </si>
   <si>
-    <t>/アカウント削除/i,</t>
+    <t>/請求明細/i,</t>
   </si>
   <si>
     <t>/このサブスクリプションを解約/i,</t>
   </si>
   <si>
-    <t>/請求明細/i,</t>
+    <t>/利用明細/i,</t>
   </si>
   <si>
     <t>/購読解除/i,</t>
   </si>
   <si>
-    <t>/利用明細/i,</t>
-  </si>
-  <si>
     <t>/最後の支払いを返して/i,</t>
   </si>
   <si>
     <t>/ダウンロードできない/i,</t>
   </si>
   <si>
+    <t>/アカウントを削除/i,</t>
+  </si>
+  <si>
     <t>/アカウントを解約/i,</t>
   </si>
   <si>
-    <t>/アカウントを削除/i,</t>
-  </si>
-  <si>
     <t>/最後の請求を返して/i,</t>
   </si>
   <si>
+    <t>/開けなかった/i,</t>
+  </si>
+  <si>
     <t>/メンバーシップを解約/i,</t>
   </si>
   <si>
-    <t>/開けなかった/i,</t>
-  </si>
-  <si>
     <t>/これを解約/i,</t>
   </si>
   <si>
+    <t>/報告された/i,</t>
+  </si>
+  <si>
     <t>/私のサブスクリプションの解約/i,</t>
   </si>
   <si>
-    <t>/報告された/i,</t>
+    <t>/請求をキャンセル/i,</t>
+  </si>
+  <si>
+    <t>/銀行に報告した/i,</t>
   </si>
   <si>
     <t>/サブスクリプションを解約中/i,</t>
   </si>
   <si>
-    <t>/請求をキャンセル/i,</t>
-  </si>
-  <si>
-    <t>/銀行に報告した/i,</t>
-  </si>
-  <si>
     <t>/Rileoのサブスクリプションを解約/i,</t>
   </si>
   <si>
     <t>/その請求をキャンセル/i,</t>
   </si>
   <si>
+    <t>/動作しない/i,</t>
+  </si>
+  <si>
     <t>/トライアルを解約/i,</t>
   </si>
   <si>
-    <t>/動作しない/i,</t>
+    <t>/モビリティプログラムのアドオン/i,</t>
   </si>
   <si>
     <t>/サブスクリプションが解約された/i,</t>
   </si>
   <si>
-    <t>/モビリティプログラムのアドオン/i,</t>
+    <t>/撤回権/i,</t>
+  </si>
+  <si>
+    <t>/アカウントの解約/i,</t>
   </si>
   <si>
     <t>/すべてのサブスクリプションを解約/i,</t>
   </si>
   <si>
-    <t>/撤回権/i,</t>
-  </si>
-  <si>
-    <t>/アカウントの解約/i,</t>
+    <t>/リセット/i,</t>
   </si>
   <si>
     <t>/アカウント解約/i,</t>
   </si>
   <si>
-    <t>/リセット/i,</t>
+    <t>/パスワード/i,</t>
   </si>
   <si>
     <t>/トライアルのサブスクリプションを解約/i,</t>
   </si>
   <si>
-    <t>/パスワード/i,</t>
+    <t>/アクセス/i,</t>
   </si>
   <si>
     <t>/メンバーシップ解約/i,</t>
   </si>
   <si>
-    <t>/アクセス/i,</t>
-  </si>
-  <si>
     <t>/新しいアカウントを作成/i,</t>
   </si>
   <si>
     <t>/ログインできない/i,</t>
   </si>
   <si>
+    <t>/使用できない/i,</t>
+  </si>
+  <si>
     <t>/サブスクリプションを停止/i,</t>
   </si>
   <si>
-    <t>/使用できない/i,</t>
+    <t>/モビリティプログラム/i,</t>
   </si>
   <si>
     <t>/Rileoのすべてのサブスクリプションを解約/i,</t>
   </si>
   <si>
-    <t>/モビリティプログラム/i,</t>
-  </si>
-  <si>
     <t>/追加の支払い/i,</t>
   </si>
   <si>
@@ -1353,10 +1380,10 @@
     <t>/アプリを解約/i,</t>
   </si>
   <si>
+    <t>＞ 退会</t>
+  </si>
+  <si>
     <t>/退会したい/i,</t>
-  </si>
-  <si>
-    <t>＞ 退会</t>
   </si>
   <si>
     <t>/(.*)?サブスクリプションを解約/i,</t>
@@ -1719,7 +1746,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="mmmm d, yyyy, h:mm am/pm"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1738,6 +1765,12 @@
       <name val="Arial"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1784,8 +1817,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
-        <bgColor rgb="FFD9EAD3"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -1840,7 +1873,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1856,34 +1889,40 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -1895,16 +1934,16 @@
     <xf borderId="0" fillId="2" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="3" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="3" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="5" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -2141,7 +2180,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="54.63"/>
+    <col customWidth="1" min="1" max="1" width="57.5"/>
     <col customWidth="1" min="2" max="2" width="28.75"/>
     <col customWidth="1" min="3" max="3" width="60.13"/>
     <col customWidth="1" min="4" max="4" width="33.75"/>
@@ -3287,7 +3326,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="4" t="s">
+      <c r="A149" s="3" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3297,1488 +3336,1555 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="3" t="s">
+      <c r="A151" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B151" s="5" t="s">
+      <c r="B151" s="6"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="6" t="s">
+      <c r="B152" s="6"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="B152" s="5"/>
+      <c r="B153" s="4"/>
     </row>
     <row r="154">
-      <c r="A154" s="7" t="s">
+      <c r="A154" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="B154" s="7" t="s">
+      <c r="B154" s="4"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="C154" s="7" t="s">
+      <c r="B155" s="4"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="D154" s="8" t="s">
+      <c r="B156" s="4"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="9" t="s">
+      <c r="B157" s="4"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="B155" s="9" t="s">
+      <c r="B158" s="4"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="C155" s="9" t="s">
+      <c r="B159" s="4"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="D155" s="10" t="s">
+      <c r="B160" s="4"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="7" t="s">
+      <c r="B161" s="4"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="B156" s="7" t="s">
+      <c r="B162" s="4"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="7"/>
+      <c r="B163" s="4"/>
+    </row>
+    <row r="164">
+      <c r="B164" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="C156" s="7" t="s">
+      <c r="C164" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="D156" s="8" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="9" t="s">
+      <c r="D164" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="B157" s="9" t="s">
+    </row>
+    <row r="165">
+      <c r="A165" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="C157" s="9" t="s">
+      <c r="B165" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="D157" s="10" t="s">
+      <c r="C165" s="10" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="7" t="s">
+      <c r="D165" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="B158" s="7" t="s">
+    </row>
+    <row r="166">
+      <c r="A166" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="C158" s="7" t="s">
+      <c r="B166" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="D158" s="8" t="s">
+      <c r="C166" s="8" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="9" t="s">
+      <c r="D166" s="9" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="B159" s="9" t="s">
+      <c r="B167" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="C159" s="9" t="s">
+      <c r="C167" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="D159" s="10" t="s">
+      <c r="D167" s="11" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="7" t="s">
+    <row r="168">
+      <c r="A168" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="B160" s="7" t="s">
+      <c r="B168" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="C160" s="7" t="s">
+      <c r="C168" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="D160" s="8" t="s">
+      <c r="D168" s="9" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="9" t="s">
+    <row r="169">
+      <c r="A169" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="B161" s="9" t="s">
+      <c r="B169" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="C161" s="9" t="s">
+      <c r="C169" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="D161" s="10" t="s">
+      <c r="D169" s="11" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="7" t="s">
+    <row r="170">
+      <c r="A170" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="B162" s="7" t="s">
+      <c r="B170" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="C162" s="7" t="s">
+      <c r="C170" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="D162" s="8" t="s">
+      <c r="D170" s="9" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="9" t="s">
+    <row r="171">
+      <c r="A171" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="B163" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="C163" s="9" t="s">
+      <c r="B171" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="D163" s="10" t="s">
+      <c r="C171" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="D171" s="11" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="B172" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="C172" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="D172" s="9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="B173" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C173" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="D173" s="11" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="B164" s="7" t="s">
+    <row r="174">
+      <c r="A174" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="B174" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="C174" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="D174" s="9" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="B175" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C175" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="D175" s="11" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="B176" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="C176" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D176" s="9" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="B177" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="C177" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="D177" s="11" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="B178" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="C178" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="D178" s="9" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="B179" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="C179" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="D179" s="11" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="B180" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="C180" s="12"/>
+      <c r="D180" s="9" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="B181" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="C181" s="13"/>
+      <c r="D181" s="11" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="B182" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="C182" s="12"/>
+      <c r="D182" s="9" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="B183" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="C183" s="13"/>
+      <c r="D183" s="11" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="B184" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="C164" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="D164" s="8" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="B165" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="C165" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="D165" s="10" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="B166" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C166" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="D166" s="8" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="B167" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="C167" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="D167" s="10" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="B168" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C168" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="D168" s="8" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="B169" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="C169" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="D169" s="10" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="B170" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="C170" s="11"/>
-      <c r="D170" s="8" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="9" t="s">
-        <v>333</v>
-      </c>
-      <c r="B171" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="C171" s="12"/>
-      <c r="D171" s="10" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="B172" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C172" s="11"/>
-      <c r="D172" s="8" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="B173" s="9" t="s">
+      <c r="C184" s="12"/>
+      <c r="D184" s="9" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="B185" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="C185" s="13"/>
+      <c r="D185" s="11" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="B186" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="C186" s="12"/>
+      <c r="D186" s="9" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="B187" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="C187" s="13"/>
+      <c r="D187" s="11" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="B188" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="C188" s="12"/>
+      <c r="D188" s="9" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="B189" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="C189" s="13"/>
+      <c r="D189" s="11" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="B190" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="C190" s="12"/>
+      <c r="D190" s="9" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="B191" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C191" s="13"/>
+      <c r="D191" s="11" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="B192" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="C192" s="12"/>
+      <c r="D192" s="9" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="B193" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="C173" s="12"/>
-      <c r="D173" s="10" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="B174" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="C174" s="11"/>
-      <c r="D174" s="8" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="B175" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="C175" s="12"/>
-      <c r="D175" s="10" t="s">
+      <c r="C193" s="13"/>
+      <c r="D193" s="11" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="B194" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="C194" s="12"/>
+      <c r="D194" s="9" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="B195" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="C195" s="13"/>
+      <c r="D195" s="11" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="B196" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="C196" s="12"/>
+      <c r="D196" s="9" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="B197" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="C197" s="13"/>
+      <c r="D197" s="11" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="B198" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="C198" s="12"/>
+      <c r="D198" s="9" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="B199" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="C199" s="13"/>
+      <c r="D199" s="11" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="B200" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="C200" s="12"/>
+      <c r="D200" s="9" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="B201" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C201" s="13"/>
+      <c r="D201" s="11" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="B202" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="C202" s="12"/>
+      <c r="D202" s="9" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="B203" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="C203" s="13"/>
+      <c r="D203" s="11" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="B204" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="C204" s="12"/>
+      <c r="D204" s="9" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="B205" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="C205" s="13"/>
+      <c r="D205" s="11" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="B206" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="C206" s="12"/>
+      <c r="D206" s="9" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="B207" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="C207" s="13"/>
+      <c r="D207" s="11" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="B208" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="C208" s="12"/>
+      <c r="D208" s="9" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="B209" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="C209" s="13"/>
+      <c r="D209" s="11" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="B210" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="C210" s="12"/>
+      <c r="D210" s="9" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="B211" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="C211" s="13"/>
+      <c r="D211" s="11" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="B212" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="C212" s="12"/>
+      <c r="D212" s="9" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="B213" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="C213" s="13"/>
+      <c r="D213" s="11" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="B214" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="C214" s="12"/>
+      <c r="D214" s="9" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="B215" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="C215" s="13"/>
+      <c r="D215" s="11" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="B216" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="C216" s="12"/>
+      <c r="D216" s="9" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="B217" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C217" s="13"/>
+      <c r="D217" s="11" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="B218" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C218" s="12"/>
+      <c r="D218" s="9" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="B219" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="C219" s="13"/>
+      <c r="D219" s="11" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="B220" s="12"/>
+      <c r="C220" s="12"/>
+      <c r="D220" s="9" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="B221" s="13"/>
+      <c r="C221" s="13"/>
+      <c r="D221" s="11" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="B176" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="C176" s="11"/>
-      <c r="D176" s="8" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="B177" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="C177" s="12"/>
-      <c r="D177" s="10" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="B178" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="C178" s="11"/>
-      <c r="D178" s="8" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="B179" s="9" t="s">
-        <v>351</v>
-      </c>
-      <c r="C179" s="12"/>
-      <c r="D179" s="10" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="B180" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="C180" s="11"/>
-      <c r="D180" s="8" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="B181" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C181" s="12"/>
-      <c r="D181" s="10" t="s">
+    <row r="222">
+      <c r="A222" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="B222" s="12"/>
+      <c r="C222" s="12"/>
+      <c r="D222" s="14"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="B223" s="13"/>
+      <c r="C223" s="13"/>
+      <c r="D223" s="15"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="B224" s="12"/>
+      <c r="C224" s="12"/>
+      <c r="D224" s="14"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="B225" s="13"/>
+      <c r="C225" s="13"/>
+      <c r="D225" s="15"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="B226" s="12"/>
+      <c r="C226" s="12"/>
+      <c r="D226" s="14"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="B227" s="13"/>
+      <c r="C227" s="13"/>
+      <c r="D227" s="15"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="B228" s="12"/>
+      <c r="C228" s="12"/>
+      <c r="D228" s="14"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="B229" s="13"/>
+      <c r="C229" s="13"/>
+      <c r="D229" s="15"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="B230" s="12"/>
+      <c r="C230" s="12"/>
+      <c r="D230" s="14"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="B231" s="13"/>
+      <c r="C231" s="13"/>
+      <c r="D231" s="15"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="B232" s="12"/>
+      <c r="C232" s="12"/>
+      <c r="D232" s="14"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="B233" s="13"/>
+      <c r="C233" s="13"/>
+      <c r="D233" s="15"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="B234" s="12"/>
+      <c r="C234" s="12"/>
+      <c r="D234" s="14"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="B235" s="13"/>
+      <c r="C235" s="13"/>
+      <c r="D235" s="15"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="B236" s="12"/>
+      <c r="C236" s="12"/>
+      <c r="D236" s="14"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="B237" s="13"/>
+      <c r="C237" s="13"/>
+      <c r="D237" s="15"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="B238" s="12"/>
+      <c r="C238" s="12"/>
+      <c r="D238" s="14"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="B239" s="13"/>
+      <c r="C239" s="13"/>
+      <c r="D239" s="15"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="B240" s="12"/>
+      <c r="C240" s="12"/>
+      <c r="D240" s="14"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="B241" s="13"/>
+      <c r="C241" s="13"/>
+      <c r="D241" s="15"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="B242" s="12"/>
+      <c r="C242" s="12"/>
+      <c r="D242" s="14"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="B243" s="13"/>
+      <c r="C243" s="13"/>
+      <c r="D243" s="15"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="B244" s="12"/>
+      <c r="C244" s="12"/>
+      <c r="D244" s="14"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="B245" s="13"/>
+      <c r="C245" s="13"/>
+      <c r="D245" s="15"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="B246" s="12"/>
+      <c r="C246" s="12"/>
+      <c r="D246" s="14"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="B247" s="13"/>
+      <c r="C247" s="13"/>
+      <c r="D247" s="15"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="B248" s="12"/>
+      <c r="C248" s="12"/>
+      <c r="D248" s="14"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="B249" s="13"/>
+      <c r="C249" s="13"/>
+      <c r="D249" s="15"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="B250" s="12"/>
+      <c r="C250" s="12"/>
+      <c r="D250" s="14"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="B251" s="13"/>
+      <c r="C251" s="13"/>
+      <c r="D251" s="15"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="B252" s="12"/>
+      <c r="C252" s="12"/>
+      <c r="D252" s="14"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="B253" s="13"/>
+      <c r="C253" s="13"/>
+      <c r="D253" s="15"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="B254" s="12"/>
+      <c r="C254" s="12"/>
+      <c r="D254" s="14"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="B255" s="13"/>
+      <c r="C255" s="13"/>
+      <c r="D255" s="15"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="B256" s="12"/>
+      <c r="C256" s="12"/>
+      <c r="D256" s="14"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="B257" s="13"/>
+      <c r="C257" s="13"/>
+      <c r="D257" s="15"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="B258" s="12"/>
+      <c r="C258" s="12"/>
+      <c r="D258" s="14"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="B259" s="13"/>
+      <c r="C259" s="13"/>
+      <c r="D259" s="15"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="B260" s="12"/>
+      <c r="C260" s="12"/>
+      <c r="D260" s="14"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="B261" s="13"/>
+      <c r="C261" s="13"/>
+      <c r="D261" s="15"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="B262" s="12"/>
+      <c r="C262" s="12"/>
+      <c r="D262" s="14"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="B263" s="13"/>
+      <c r="C263" s="13"/>
+      <c r="D263" s="15"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="B264" s="12"/>
+      <c r="C264" s="12"/>
+      <c r="D264" s="14"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="B265" s="13"/>
+      <c r="C265" s="13"/>
+      <c r="D265" s="15"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="B266" s="12"/>
+      <c r="C266" s="12"/>
+      <c r="D266" s="14"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="B267" s="13"/>
+      <c r="C267" s="13"/>
+      <c r="D267" s="15"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="B268" s="12"/>
+      <c r="C268" s="12"/>
+      <c r="D268" s="14"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="B269" s="13"/>
+      <c r="C269" s="13"/>
+      <c r="D269" s="15"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="B270" s="12"/>
+      <c r="C270" s="12"/>
+      <c r="D270" s="14"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="B271" s="13"/>
+      <c r="C271" s="13"/>
+      <c r="D271" s="15"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="B272" s="12"/>
+      <c r="C272" s="12"/>
+      <c r="D272" s="14"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="B273" s="13"/>
+      <c r="C273" s="13"/>
+      <c r="D273" s="15"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="B274" s="12"/>
+      <c r="C274" s="12"/>
+      <c r="D274" s="14"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B275" s="13"/>
+      <c r="C275" s="13"/>
+      <c r="D275" s="15"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="B276" s="12"/>
+      <c r="C276" s="12"/>
+      <c r="D276" s="14"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="B277" s="13"/>
+      <c r="C277" s="13"/>
+      <c r="D277" s="15"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="B278" s="12"/>
+      <c r="C278" s="12"/>
+      <c r="D278" s="14"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="B279" s="13"/>
+      <c r="C279" s="13"/>
+      <c r="D279" s="15"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="B280" s="12"/>
+      <c r="C280" s="12"/>
+      <c r="D280" s="14"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="B281" s="13"/>
+      <c r="C281" s="13"/>
+      <c r="D281" s="15"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="B282" s="12"/>
+      <c r="C282" s="12"/>
+      <c r="D282" s="14"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="8" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="B182" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C182" s="11"/>
-      <c r="D182" s="8" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="B183" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="C183" s="12"/>
-      <c r="D183" s="10" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="B184" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C184" s="11"/>
-      <c r="D184" s="8" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="B185" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="C185" s="12"/>
-      <c r="D185" s="10" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="B186" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="C186" s="11"/>
-      <c r="D186" s="8" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="B187" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="C187" s="12"/>
-      <c r="D187" s="10" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="B188" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="C188" s="11"/>
-      <c r="D188" s="8" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="B189" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="C189" s="12"/>
-      <c r="D189" s="10" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="B190" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="C190" s="11"/>
-      <c r="D190" s="8" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="B191" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="C191" s="12"/>
-      <c r="D191" s="10" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="B192" s="7" t="s">
+      <c r="B283" s="13"/>
+      <c r="C283" s="13"/>
+      <c r="D283" s="15"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="B284" s="12"/>
+      <c r="C284" s="12"/>
+      <c r="D284" s="14"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="B285" s="13"/>
+      <c r="C285" s="13"/>
+      <c r="D285" s="15"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="10" t="s">
         <v>373</v>
       </c>
-      <c r="C192" s="11"/>
-      <c r="D192" s="8" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="B193" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="C193" s="12"/>
-      <c r="D193" s="10" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="B194" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="C194" s="11"/>
-      <c r="D194" s="8" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="B195" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="C195" s="12"/>
-      <c r="D195" s="10" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="B196" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="C196" s="11"/>
-      <c r="D196" s="8" t="s">
+      <c r="B286" s="12"/>
+      <c r="C286" s="12"/>
+      <c r="D286" s="14"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="B287" s="13"/>
+      <c r="C287" s="13"/>
+      <c r="D287" s="15"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="B288" s="12"/>
+      <c r="C288" s="12"/>
+      <c r="D288" s="14"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="B289" s="13"/>
+      <c r="C289" s="13"/>
+      <c r="D289" s="15"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="B290" s="12"/>
+      <c r="C290" s="12"/>
+      <c r="D290" s="14"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="B291" s="13"/>
+      <c r="C291" s="13"/>
+      <c r="D291" s="15"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="B292" s="12"/>
+      <c r="C292" s="12"/>
+      <c r="D292" s="14"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="B293" s="13"/>
+      <c r="C293" s="13"/>
+      <c r="D293" s="15"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="B294" s="12"/>
+      <c r="C294" s="12"/>
+      <c r="D294" s="14"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="B295" s="13"/>
+      <c r="C295" s="13"/>
+      <c r="D295" s="15"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="B296" s="12"/>
+      <c r="C296" s="12"/>
+      <c r="D296" s="14"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="B297" s="13"/>
+      <c r="C297" s="13"/>
+      <c r="D297" s="15"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="B298" s="12"/>
+      <c r="C298" s="12"/>
+      <c r="D298" s="14"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="B299" s="13"/>
+      <c r="C299" s="13"/>
+      <c r="D299" s="15"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="B300" s="12"/>
+      <c r="C300" s="12"/>
+      <c r="D300" s="14"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="B301" s="13"/>
+      <c r="C301" s="13"/>
+      <c r="D301" s="15"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="B302" s="12"/>
+      <c r="C302" s="12"/>
+      <c r="D302" s="14"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="B303" s="13"/>
+      <c r="C303" s="13"/>
+      <c r="D303" s="15"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="B304" s="12"/>
+      <c r="C304" s="12"/>
+      <c r="D304" s="14"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B305" s="13"/>
+      <c r="C305" s="13"/>
+      <c r="D305" s="15"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="B306" s="12"/>
+      <c r="C306" s="12"/>
+      <c r="D306" s="14"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B307" s="13"/>
+      <c r="C307" s="13"/>
+      <c r="D307" s="15"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="B308" s="12"/>
+      <c r="C308" s="12"/>
+      <c r="D308" s="14"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B309" s="13"/>
+      <c r="C309" s="13"/>
+      <c r="D309" s="15"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="B310" s="12"/>
+      <c r="C310" s="12"/>
+      <c r="D310" s="14"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="B311" s="13"/>
+      <c r="C311" s="13"/>
+      <c r="D311" s="15"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="10" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="B197" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="C197" s="12"/>
-      <c r="D197" s="10" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="B198" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="C198" s="11"/>
-      <c r="D198" s="8" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="B199" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="C199" s="12"/>
-      <c r="D199" s="10" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="B200" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C200" s="11"/>
-      <c r="D200" s="8" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="B201" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="C201" s="12"/>
-      <c r="D201" s="10" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="B202" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C202" s="11"/>
-      <c r="D202" s="8" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="B203" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="C203" s="12"/>
-      <c r="D203" s="10" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="B204" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="C204" s="11"/>
-      <c r="D204" s="8" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="B205" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="C205" s="12"/>
-      <c r="D205" s="10" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="B206" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="C206" s="11"/>
-      <c r="D206" s="8" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="B207" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="C207" s="12"/>
-      <c r="D207" s="10" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="B208" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="C208" s="11"/>
-      <c r="D208" s="8" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="B209" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="C209" s="12"/>
-      <c r="D209" s="10" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="B210" s="11"/>
-      <c r="C210" s="11"/>
-      <c r="D210" s="8" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="B211" s="12"/>
-      <c r="C211" s="12"/>
-      <c r="D211" s="10" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="B212" s="11"/>
-      <c r="C212" s="11"/>
-      <c r="D212" s="13"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="B213" s="12"/>
-      <c r="C213" s="12"/>
-      <c r="D213" s="14"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="B214" s="11"/>
-      <c r="C214" s="11"/>
-      <c r="D214" s="13"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="B215" s="12"/>
-      <c r="C215" s="12"/>
-      <c r="D215" s="14"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="B216" s="11"/>
-      <c r="C216" s="11"/>
-      <c r="D216" s="13"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="B217" s="12"/>
-      <c r="C217" s="12"/>
-      <c r="D217" s="14"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="B218" s="11"/>
-      <c r="C218" s="11"/>
-      <c r="D218" s="13"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="B219" s="12"/>
-      <c r="C219" s="12"/>
-      <c r="D219" s="14"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="B220" s="11"/>
-      <c r="C220" s="11"/>
-      <c r="D220" s="13"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="B221" s="12"/>
-      <c r="C221" s="12"/>
-      <c r="D221" s="14"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="B222" s="11"/>
-      <c r="C222" s="11"/>
-      <c r="D222" s="13"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="B223" s="12"/>
-      <c r="C223" s="12"/>
-      <c r="D223" s="14"/>
-    </row>
-    <row r="224">
-      <c r="A224" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="B224" s="11"/>
-      <c r="C224" s="11"/>
-      <c r="D224" s="13"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="B225" s="12"/>
-      <c r="C225" s="12"/>
-      <c r="D225" s="14"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="B226" s="11"/>
-      <c r="C226" s="11"/>
-      <c r="D226" s="13"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="B227" s="12"/>
-      <c r="C227" s="12"/>
-      <c r="D227" s="14"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="B228" s="11"/>
-      <c r="C228" s="11"/>
-      <c r="D228" s="13"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="B229" s="12"/>
-      <c r="C229" s="12"/>
-      <c r="D229" s="14"/>
-    </row>
-    <row r="230">
-      <c r="A230" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="B230" s="11"/>
-      <c r="C230" s="11"/>
-      <c r="D230" s="13"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="B231" s="12"/>
-      <c r="C231" s="12"/>
-      <c r="D231" s="14"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="B232" s="11"/>
-      <c r="C232" s="11"/>
-      <c r="D232" s="13"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="B233" s="12"/>
-      <c r="C233" s="12"/>
-      <c r="D233" s="14"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="B234" s="11"/>
-      <c r="C234" s="11"/>
-      <c r="D234" s="13"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="B235" s="12"/>
-      <c r="C235" s="12"/>
-      <c r="D235" s="14"/>
-    </row>
-    <row r="236">
-      <c r="A236" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="B236" s="11"/>
-      <c r="C236" s="11"/>
-      <c r="D236" s="13"/>
-    </row>
-    <row r="237">
-      <c r="A237" s="9" t="s">
-        <v>418</v>
-      </c>
-      <c r="B237" s="12"/>
-      <c r="C237" s="12"/>
-      <c r="D237" s="14"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="B238" s="11"/>
-      <c r="C238" s="11"/>
-      <c r="D238" s="13"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="B239" s="12"/>
-      <c r="C239" s="12"/>
-      <c r="D239" s="14"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B240" s="11"/>
-      <c r="C240" s="11"/>
-      <c r="D240" s="13"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="B241" s="12"/>
-      <c r="C241" s="12"/>
-      <c r="D241" s="14"/>
-    </row>
-    <row r="242">
-      <c r="A242" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="B242" s="11"/>
-      <c r="C242" s="11"/>
-      <c r="D242" s="13"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="B243" s="12"/>
-      <c r="C243" s="12"/>
-      <c r="D243" s="14"/>
-    </row>
-    <row r="244">
-      <c r="A244" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="B244" s="11"/>
-      <c r="C244" s="11"/>
-      <c r="D244" s="13"/>
-    </row>
-    <row r="245">
-      <c r="A245" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="B245" s="12"/>
-      <c r="C245" s="12"/>
-      <c r="D245" s="14"/>
-    </row>
-    <row r="246">
-      <c r="A246" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="B246" s="11"/>
-      <c r="C246" s="11"/>
-      <c r="D246" s="13"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="B247" s="12"/>
-      <c r="C247" s="12"/>
-      <c r="D247" s="14"/>
-    </row>
-    <row r="248">
-      <c r="A248" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="B248" s="11"/>
-      <c r="C248" s="11"/>
-      <c r="D248" s="13"/>
-    </row>
-    <row r="249">
-      <c r="A249" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="B249" s="12"/>
-      <c r="C249" s="12"/>
-      <c r="D249" s="14"/>
-    </row>
-    <row r="250">
-      <c r="A250" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="B250" s="11"/>
-      <c r="C250" s="11"/>
-      <c r="D250" s="13"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="B251" s="12"/>
-      <c r="C251" s="12"/>
-      <c r="D251" s="14"/>
-    </row>
-    <row r="252">
-      <c r="A252" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="B252" s="11"/>
-      <c r="C252" s="11"/>
-      <c r="D252" s="13"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="B253" s="12"/>
-      <c r="C253" s="12"/>
-      <c r="D253" s="14"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="B254" s="11"/>
-      <c r="C254" s="11"/>
-      <c r="D254" s="13"/>
-    </row>
-    <row r="255">
-      <c r="A255" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="B255" s="12"/>
-      <c r="C255" s="12"/>
-      <c r="D255" s="14"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="B256" s="11"/>
-      <c r="C256" s="11"/>
-      <c r="D256" s="13"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="B257" s="12"/>
-      <c r="C257" s="12"/>
-      <c r="D257" s="14"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="B258" s="11"/>
-      <c r="C258" s="11"/>
-      <c r="D258" s="13"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="B259" s="12"/>
-      <c r="C259" s="12"/>
-      <c r="D259" s="14"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="7" t="s">
-        <v>428</v>
-      </c>
-      <c r="B260" s="11"/>
-      <c r="C260" s="11"/>
-      <c r="D260" s="13"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="B261" s="12"/>
-      <c r="C261" s="12"/>
-      <c r="D261" s="14"/>
-    </row>
-    <row r="262">
-      <c r="A262" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="B262" s="11"/>
-      <c r="C262" s="11"/>
-      <c r="D262" s="13"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="9" t="s">
+      <c r="B312" s="12"/>
+      <c r="C312" s="12"/>
+      <c r="D312" s="14"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="B263" s="12"/>
-      <c r="C263" s="12"/>
-      <c r="D263" s="14"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="B264" s="11"/>
-      <c r="C264" s="11"/>
-      <c r="D264" s="13"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="B265" s="12"/>
-      <c r="C265" s="12"/>
-      <c r="D265" s="14"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="B266" s="11"/>
-      <c r="C266" s="11"/>
-      <c r="D266" s="13"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="B267" s="12"/>
-      <c r="C267" s="12"/>
-      <c r="D267" s="14"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="B268" s="11"/>
-      <c r="C268" s="11"/>
-      <c r="D268" s="13"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="B269" s="12"/>
-      <c r="C269" s="12"/>
-      <c r="D269" s="14"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="7" t="s">
-        <v>432</v>
-      </c>
-      <c r="B270" s="11"/>
-      <c r="C270" s="11"/>
-      <c r="D270" s="13"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="9" t="s">
-        <v>433</v>
-      </c>
-      <c r="B271" s="12"/>
-      <c r="C271" s="12"/>
-      <c r="D271" s="14"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="B272" s="11"/>
-      <c r="C272" s="11"/>
-      <c r="D272" s="13"/>
-    </row>
-    <row r="273">
-      <c r="A273" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="B273" s="12"/>
-      <c r="C273" s="12"/>
-      <c r="D273" s="14"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="B274" s="11"/>
-      <c r="C274" s="11"/>
-      <c r="D274" s="13"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="B275" s="12"/>
-      <c r="C275" s="12"/>
-      <c r="D275" s="14"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="7" t="s">
-        <v>431</v>
-      </c>
-      <c r="B276" s="11"/>
-      <c r="C276" s="11"/>
-      <c r="D276" s="13"/>
-    </row>
-    <row r="277">
-      <c r="A277" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="B277" s="12"/>
-      <c r="C277" s="12"/>
-      <c r="D277" s="14"/>
-    </row>
-    <row r="278">
-      <c r="A278" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="B278" s="11"/>
-      <c r="C278" s="11"/>
-      <c r="D278" s="13"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="B279" s="12"/>
-      <c r="C279" s="12"/>
-      <c r="D279" s="14"/>
-    </row>
-    <row r="280">
-      <c r="A280" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="B280" s="11"/>
-      <c r="C280" s="11"/>
-      <c r="D280" s="13"/>
-    </row>
-    <row r="281">
-      <c r="A281" s="9" t="s">
-        <v>437</v>
-      </c>
-      <c r="B281" s="12"/>
-      <c r="C281" s="12"/>
-      <c r="D281" s="14"/>
-    </row>
-    <row r="282">
-      <c r="A282" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="B282" s="11"/>
-      <c r="C282" s="11"/>
-      <c r="D282" s="13"/>
-    </row>
-    <row r="283">
-      <c r="A283" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="B283" s="12"/>
-      <c r="C283" s="12"/>
-      <c r="D283" s="14"/>
-    </row>
-    <row r="284">
-      <c r="A284" s="7" t="s">
-        <v>437</v>
-      </c>
-      <c r="B284" s="11"/>
-      <c r="C284" s="11"/>
-      <c r="D284" s="13"/>
-    </row>
-    <row r="285">
-      <c r="A285" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="B285" s="12"/>
-      <c r="C285" s="12"/>
-      <c r="D285" s="14"/>
-    </row>
-    <row r="286">
-      <c r="A286" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="B286" s="11"/>
-      <c r="C286" s="11"/>
-      <c r="D286" s="13"/>
-    </row>
-    <row r="287">
-      <c r="A287" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="B287" s="12"/>
-      <c r="C287" s="12"/>
-      <c r="D287" s="14"/>
-    </row>
-    <row r="288">
-      <c r="A288" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="B288" s="11"/>
-      <c r="C288" s="11"/>
-      <c r="D288" s="13"/>
-    </row>
-    <row r="289">
-      <c r="A289" s="9" t="s">
-        <v>440</v>
-      </c>
-      <c r="B289" s="12"/>
-      <c r="C289" s="12"/>
-      <c r="D289" s="14"/>
-    </row>
-    <row r="290">
-      <c r="A290" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="B290" s="11"/>
-      <c r="C290" s="11"/>
-      <c r="D290" s="13"/>
-    </row>
-    <row r="291">
-      <c r="A291" s="9" t="s">
-        <v>442</v>
-      </c>
-      <c r="B291" s="12"/>
-      <c r="C291" s="12"/>
-      <c r="D291" s="14"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="B292" s="11"/>
-      <c r="C292" s="11"/>
-      <c r="D292" s="13"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="B293" s="12"/>
-      <c r="C293" s="12"/>
-      <c r="D293" s="14"/>
-    </row>
-    <row r="294">
-      <c r="A294" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="B294" s="11"/>
-      <c r="C294" s="11"/>
-      <c r="D294" s="13"/>
-    </row>
-    <row r="295">
-      <c r="A295" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="B295" s="12"/>
-      <c r="C295" s="12"/>
-      <c r="D295" s="14"/>
-    </row>
-    <row r="296">
-      <c r="A296" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="B296" s="11"/>
-      <c r="C296" s="11"/>
-      <c r="D296" s="13"/>
-    </row>
-    <row r="297">
-      <c r="A297" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="B297" s="12"/>
-      <c r="C297" s="12"/>
-      <c r="D297" s="14"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="B298" s="11"/>
-      <c r="C298" s="11"/>
-      <c r="D298" s="13"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="B299" s="12"/>
-      <c r="C299" s="12"/>
-      <c r="D299" s="14"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="B300" s="11"/>
-      <c r="C300" s="11"/>
-      <c r="D300" s="13"/>
-    </row>
-    <row r="301">
-      <c r="A301" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="B301" s="12"/>
-      <c r="C301" s="12"/>
-      <c r="D301" s="14"/>
-    </row>
-    <row r="302">
-      <c r="A302" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="B302" s="11"/>
-      <c r="C302" s="11"/>
-      <c r="D302" s="13"/>
-    </row>
-    <row r="303">
-      <c r="A303" s="9" t="s">
-        <v>446</v>
-      </c>
-      <c r="B303" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="C303" s="12"/>
-      <c r="D303" s="14"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="B304" s="11"/>
-      <c r="C304" s="11"/>
-      <c r="D304" s="13"/>
+      <c r="B313" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="C313" s="13"/>
+      <c r="D313" s="15"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="B314" s="12"/>
+      <c r="C314" s="12"/>
+      <c r="D314" s="14"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="B315" s="16"/>
+      <c r="C315" s="16"/>
+      <c r="D315" s="16"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -4799,1342 +4905,1342 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="C2" s="4">
         <v>2.9676421809298E13</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="17">
         <v>45923.0</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C3" s="4">
         <v>3.0725212248466E13</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="17">
         <v>45963.0</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C4" s="4">
         <v>3.0365754086162E13</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="17">
         <v>45950.0</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C5" s="4">
         <v>3.3224588062482E13</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="17">
         <v>46063.0</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C6" s="4">
         <v>2.8128124121874E13</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="17">
         <v>45854.0</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="s">
-        <v>465</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>463</v>
-      </c>
-      <c r="C7" s="16">
+      <c r="A7" s="18" t="s">
+        <v>474</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="C7" s="18">
         <v>2.086250911093E13</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="19">
         <v>45524.0</v>
       </c>
-      <c r="E7" s="16" t="s">
-        <v>466</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>467</v>
+      <c r="E7" s="18" t="s">
+        <v>475</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C8" s="4">
         <v>3.1029083512594E13</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="17">
         <v>45974.0</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>469</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>460</v>
       </c>
       <c r="C9" s="4">
         <v>3.0725249206034E13</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="17">
         <v>45963.0</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C10" s="4">
         <v>3.0411884385938E13</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="17">
         <v>45951.0</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C11" s="4">
         <v>3.395585630389E13</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="17">
         <v>46092.0</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C12" s="4">
         <v>3.3955844058258E13</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="17">
         <v>46092.0</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C13" s="4">
         <v>3.1029096994578E13</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="17">
         <v>45974.0</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C14" s="4">
         <v>2.9771989621778E13</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="17">
         <v>45926.0</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="C15" s="4">
         <v>2.5140861016082E13</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="17">
         <v>45722.0</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C16" s="4">
         <v>2.904937130101E13</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="17">
         <v>45905.0</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="C17" s="4">
         <v>2.0862509097106E13</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="17">
         <v>45524.0</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C18" s="4">
         <v>2.3503248732818E13</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="17">
         <v>45650.0</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C19" s="4">
         <v>2.9771995259154E13</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="17">
         <v>45926.0</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="C20" s="4">
         <v>3.5038938188306E13</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="17">
         <v>46135.0</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C21" s="4">
         <v>3.4125196939154E13</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="17">
         <v>46099.0</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C22" s="4">
         <v>3.5039054408082E13</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="17">
         <v>46135.0</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C23" s="4">
         <v>3.1028915702546E13</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="17">
         <v>45974.0</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="s">
-        <v>485</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>463</v>
-      </c>
-      <c r="C24" s="16">
+      <c r="A24" s="18" t="s">
+        <v>494</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="C24" s="18">
         <v>2.0862509109266E13</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="19">
         <v>45524.0</v>
       </c>
-      <c r="E24" s="16" t="s">
-        <v>466</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>467</v>
+      <c r="E24" s="18" t="s">
+        <v>475</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C25" s="4">
         <v>3.5038775325202E13</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="17">
         <v>46135.0</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="C26" s="4">
         <v>3.503898421173E13</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="17">
         <v>46135.0</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C27" s="4">
         <v>3.041689677109E13</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="17">
         <v>45951.0</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="C28" s="4">
         <v>2.440784220405E13</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="17">
         <v>45692.0</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C29" s="4">
         <v>2.499424266997E13</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="17">
         <v>45716.0</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C30" s="4">
         <v>3.4514436622354E13</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="17">
         <v>46114.0</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C31" s="4">
         <v>3.0970975231506E13</v>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="17">
         <v>45972.0</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C32" s="4">
         <v>3.3200330000658E13</v>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="17">
         <v>46062.0</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="C33" s="4">
         <v>2.5211065907346E13</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="17">
         <v>45727.0</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C34" s="4">
         <v>3.3955840192146E13</v>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="17">
         <v>46092.0</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C35" s="4">
         <v>2.9772052523154E13</v>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="17">
         <v>45926.0</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C36" s="4">
         <v>2.125082728885E13</v>
       </c>
-      <c r="D36" s="15">
+      <c r="D36" s="17">
         <v>46104.0</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C37" s="4">
         <v>3.5038652960402E13</v>
       </c>
-      <c r="D37" s="15">
+      <c r="D37" s="17">
         <v>46135.0</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C38" s="4">
         <v>3.1368685562002E13</v>
       </c>
-      <c r="D38" s="15">
+      <c r="D38" s="17">
         <v>45987.0</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="C39" s="4">
         <v>3.5038986006674E13</v>
       </c>
-      <c r="D39" s="15">
+      <c r="D39" s="17">
         <v>46135.0</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C40" s="4">
         <v>2.086251419637E13</v>
       </c>
-      <c r="D40" s="15">
+      <c r="D40" s="17">
         <v>45524.0</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="s">
-        <v>502</v>
-      </c>
-      <c r="B41" s="16" t="s">
-        <v>463</v>
-      </c>
-      <c r="C41" s="16">
+      <c r="A41" s="18" t="s">
+        <v>511</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="C41" s="18">
         <v>2.1250680239762E13</v>
       </c>
-      <c r="D41" s="17">
+      <c r="D41" s="19">
         <v>46148.0</v>
       </c>
-      <c r="E41" s="16" t="s">
-        <v>457</v>
-      </c>
-      <c r="F41" s="16" t="s">
-        <v>467</v>
+      <c r="E41" s="18" t="s">
+        <v>466</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C42" s="4">
         <v>3.102905894453E13</v>
       </c>
-      <c r="D42" s="15">
+      <c r="D42" s="17">
         <v>45974.0</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C43" s="4">
         <v>3.5038213809426E13</v>
       </c>
-      <c r="D43" s="15">
+      <c r="D43" s="17">
         <v>46135.0</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="C44" s="4">
         <v>3.503895689077E13</v>
       </c>
-      <c r="D44" s="15">
+      <c r="D44" s="17">
         <v>46135.0</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="C45" s="4">
         <v>2.1250842116626E13</v>
       </c>
-      <c r="D45" s="15">
+      <c r="D45" s="17">
         <v>46141.0</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C46" s="4">
         <v>2.321857987125E13</v>
       </c>
-      <c r="D46" s="15">
+      <c r="D46" s="17">
         <v>45730.0</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C47" s="4">
         <v>2.6367127460498E13</v>
       </c>
-      <c r="D47" s="15">
+      <c r="D47" s="17">
         <v>45776.0</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="s">
-        <v>509</v>
-      </c>
-      <c r="B48" s="16" t="s">
-        <v>463</v>
-      </c>
-      <c r="C48" s="16">
+      <c r="A48" s="18" t="s">
+        <v>518</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="C48" s="18">
         <v>2.1201306990354E13</v>
       </c>
-      <c r="D48" s="17">
+      <c r="D48" s="19">
         <v>46153.0</v>
       </c>
-      <c r="E48" s="16" t="s">
-        <v>457</v>
-      </c>
-      <c r="F48" s="16" t="s">
-        <v>467</v>
+      <c r="E48" s="18" t="s">
+        <v>466</v>
+      </c>
+      <c r="F48" s="18" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C49" s="4">
         <v>3.5018413849362E13</v>
       </c>
-      <c r="D49" s="15">
+      <c r="D49" s="17">
         <v>46134.0</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C50" s="4">
         <v>3.082432269493E13</v>
       </c>
-      <c r="D50" s="15">
+      <c r="D50" s="17">
         <v>45966.0</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="C51" s="4">
         <v>3.5039050046866E13</v>
       </c>
-      <c r="D51" s="15">
+      <c r="D51" s="17">
         <v>46135.0</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C52" s="4">
         <v>3.3955841621266E13</v>
       </c>
-      <c r="D52" s="15">
+      <c r="D52" s="17">
         <v>46092.0</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="C53" s="4">
         <v>2.2016222537234E13</v>
       </c>
-      <c r="D53" s="15">
+      <c r="D53" s="17">
         <v>45671.0</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C54" s="4">
         <v>3.4541093094802E13</v>
       </c>
-      <c r="D54" s="15">
+      <c r="D54" s="17">
         <v>46115.0</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="C55" s="4">
         <v>3.454104964981E13</v>
       </c>
-      <c r="D55" s="15">
+      <c r="D55" s="17">
         <v>46141.0</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="C56" s="4">
         <v>2.1250903271954E13</v>
       </c>
-      <c r="D56" s="15">
+      <c r="D56" s="17">
         <v>45544.0</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C57" s="4">
         <v>2.9771972975122E13</v>
       </c>
-      <c r="D57" s="15">
+      <c r="D57" s="17">
         <v>45926.0</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C58" s="4">
         <v>2.0862514183058E13</v>
       </c>
-      <c r="D58" s="15">
+      <c r="D58" s="17">
         <v>45524.0</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C59" s="4">
         <v>3.3955827087122E13</v>
       </c>
-      <c r="D59" s="15">
+      <c r="D59" s="17">
         <v>46092.0</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C60" s="4">
         <v>3.102912725365E13</v>
       </c>
-      <c r="D60" s="15">
+      <c r="D60" s="17">
         <v>45974.0</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C61" s="4">
         <v>2.1250939822354E13</v>
       </c>
-      <c r="D61" s="15">
+      <c r="D61" s="17">
         <v>45544.0</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="s">
-        <v>523</v>
-      </c>
-      <c r="B62" s="16" t="s">
-        <v>463</v>
-      </c>
-      <c r="C62" s="16">
+      <c r="A62" s="18" t="s">
+        <v>532</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="C62" s="18">
         <v>2.0862514191506E13</v>
       </c>
-      <c r="D62" s="17">
+      <c r="D62" s="19">
         <v>45524.0</v>
       </c>
-      <c r="E62" s="16" t="s">
-        <v>466</v>
-      </c>
-      <c r="F62" s="16" t="s">
-        <v>467</v>
+      <c r="E62" s="18" t="s">
+        <v>475</v>
+      </c>
+      <c r="F62" s="18" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="C63" s="4">
         <v>2.7433474056978E13</v>
       </c>
-      <c r="D63" s="15">
+      <c r="D63" s="17">
         <v>45824.0</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C64" s="4">
         <v>3.445617546613E13</v>
       </c>
-      <c r="D64" s="15">
+      <c r="D64" s="17">
         <v>46112.0</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C65" s="4">
         <v>3.445631659509E13</v>
       </c>
-      <c r="D65" s="15">
+      <c r="D65" s="17">
         <v>46112.0</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C66" s="4">
         <v>2.086254321461E13</v>
       </c>
-      <c r="D66" s="15">
+      <c r="D66" s="17">
         <v>45524.0</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="C67" s="4">
         <v>2.7433474056338E13</v>
       </c>
-      <c r="D67" s="15">
+      <c r="D67" s="17">
         <v>45824.0</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="68">
@@ -6142,159 +6248,159 @@
         <v>2</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="C68" s="4">
         <v>3.503887818933E13</v>
       </c>
-      <c r="D68" s="15">
+      <c r="D68" s="17">
         <v>46135.0</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C69" s="4">
         <v>3.041182882037E13</v>
       </c>
-      <c r="D69" s="15">
+      <c r="D69" s="17">
         <v>45951.0</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C70" s="4">
         <v>2.0862514193426E13</v>
       </c>
-      <c r="D70" s="15">
+      <c r="D70" s="17">
         <v>45524.0</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C71" s="4">
         <v>3.0416876887826E13</v>
       </c>
-      <c r="D71" s="15">
+      <c r="D71" s="17">
         <v>45951.0</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C72" s="4">
         <v>3.0416887609234E13</v>
       </c>
-      <c r="D72" s="15">
+      <c r="D72" s="17">
         <v>45951.0</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="C73" s="4">
         <v>3.3249444208786E13</v>
       </c>
-      <c r="D73" s="15">
+      <c r="D73" s="17">
         <v>46097.0</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="C74" s="4">
         <v>2.1250891277458E13</v>
       </c>
-      <c r="D74" s="15">
+      <c r="D74" s="17">
         <v>45544.0</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C75" s="4">
         <v>3.1368973395474E13</v>
       </c>
-      <c r="D75" s="15">
+      <c r="D75" s="17">
         <v>45987.0</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -6317,86 +6423,86 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="s">
-        <v>537</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>538</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>539</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>540</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>541</v>
+      <c r="A1" s="20" t="s">
+        <v>546</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>547</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>548</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>549</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="s">
-        <v>542</v>
-      </c>
-      <c r="B2" s="20">
+      <c r="A2" s="21" t="s">
+        <v>551</v>
+      </c>
+      <c r="B2" s="22">
         <v>46155.782638888886</v>
       </c>
-      <c r="C2" s="21" t="s">
-        <v>543</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>544</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>545</v>
+      <c r="C2" s="23" t="s">
+        <v>552</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>553</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="s">
-        <v>546</v>
-      </c>
-      <c r="B3" s="20">
+      <c r="A3" s="24" t="s">
+        <v>555</v>
+      </c>
+      <c r="B3" s="22">
         <v>46155.78472222222</v>
       </c>
-      <c r="C3" s="22" t="s">
-        <v>547</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>548</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>545</v>
+      <c r="C3" s="24" t="s">
+        <v>556</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="s">
-        <v>549</v>
-      </c>
-      <c r="B4" s="23">
+      <c r="A4" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B4" s="25">
         <v>46148.686111111114</v>
       </c>
-      <c r="C4" s="22" t="s">
-        <v>550</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>551</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>545</v>
+      <c r="C4" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
+      <c r="A5" s="26"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
     </row>
     <row r="6">
-      <c r="A6" s="24"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
+      <c r="A6" s="26"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
     </row>
   </sheetData>
   <printOptions/>

--- a/rileo_data_enrichment.xlsx
+++ b/rileo_data_enrichment.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="563">
   <si>
     <t>Cancel</t>
   </si>
@@ -865,6 +865,12 @@
   </si>
   <si>
     <t>/non voglio (più )?(l')?abbonamento/i,</t>
+  </si>
+  <si>
+    <t>/disdetta (dell')?abbonamento/i,</t>
+  </si>
+  <si>
+    <t>/annull\w*(.*)?(abbonamento|servizio|contratto)/i,</t>
   </si>
   <si>
     <t>/返金/i,</t>
@@ -1746,7 +1752,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="mmmm d, yyyy, h:mm am/pm"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1776,13 +1782,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="10.0"/>
       <color rgb="FF202124"/>
       <name val="&quot;Noto Sans JP&quot;"/>
     </font>
     <font>
       <sz val="12.0"/>
       <color rgb="FF000000"/>
+      <name val="&quot;Noto Sans JP&quot;"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF202124"/>
       <name val="&quot;Noto Sans JP&quot;"/>
     </font>
     <font>
@@ -1802,7 +1813,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1819,6 +1830,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
@@ -1873,7 +1890,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1895,34 +1912,37 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="top"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="2" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="2" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -1934,16 +1954,16 @@
     <xf borderId="0" fillId="2" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="3" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="3" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="6" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -3408,1483 +3428,1499 @@
       <c r="B162" s="4"/>
     </row>
     <row r="163">
-      <c r="A163" s="7"/>
-      <c r="B163" s="4"/>
+      <c r="A163" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="B163" s="8"/>
+      <c r="C163" s="8"/>
+      <c r="D163" s="8"/>
     </row>
     <row r="164">
-      <c r="B164" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="C164" s="8" t="s">
+      <c r="A164" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="D164" s="9" t="s">
+      <c r="B164" s="8"/>
+      <c r="C164" s="8"/>
+      <c r="D164" s="8"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="9"/>
+      <c r="B165" s="4"/>
+    </row>
+    <row r="166">
+      <c r="B166" s="10" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="8" t="s">
+      <c r="C166" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="B165" s="10" t="s">
+      <c r="D166" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="C165" s="10" t="s">
+    </row>
+    <row r="167">
+      <c r="A167" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="D165" s="11" t="s">
+      <c r="B167" s="12" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="10" t="s">
+      <c r="C167" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="B166" s="8" t="s">
+      <c r="D167" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="C166" s="8" t="s">
+    </row>
+    <row r="168">
+      <c r="A168" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="D166" s="9" t="s">
+      <c r="B168" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="C168" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="D168" s="11" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="B169" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="C169" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="D169" s="13" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="B170" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="C170" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="D170" s="11" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="B171" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="C171" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="D171" s="13" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="B172" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="C172" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="D172" s="11" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="B173" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="C173" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="D173" s="13" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="B174" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C174" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="D174" s="11" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="B175" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="C175" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="D175" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="B176" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="C176" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="D176" s="11" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="B177" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="C177" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="D177" s="13" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="B178" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="C178" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="D178" s="11" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="B179" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="C179" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="D179" s="13" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="B180" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="C180" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="D180" s="11" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="B181" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="C181" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="D181" s="13" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="B182" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="C182" s="14"/>
+      <c r="D182" s="11" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="B183" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="C183" s="15"/>
+      <c r="D183" s="13" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="B184" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="C184" s="14"/>
+      <c r="D184" s="11" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="B185" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="C185" s="15"/>
+      <c r="D185" s="13" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="B186" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="C186" s="14"/>
+      <c r="D186" s="11" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="B187" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="C187" s="15"/>
+      <c r="D187" s="13" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B188" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="C188" s="14"/>
+      <c r="D188" s="11" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="B189" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="C189" s="15"/>
+      <c r="D189" s="13" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="B190" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C190" s="14"/>
+      <c r="D190" s="11" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="B191" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="C191" s="15"/>
+      <c r="D191" s="13" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="B192" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="C192" s="14"/>
+      <c r="D192" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="B193" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C193" s="15"/>
+      <c r="D193" s="13" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="B194" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="C194" s="14"/>
+      <c r="D194" s="11" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="B195" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="C195" s="15"/>
+      <c r="D195" s="13" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="B196" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="C196" s="14"/>
+      <c r="D196" s="11" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="B197" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="C197" s="15"/>
+      <c r="D197" s="13" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="B198" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="C198" s="14"/>
+      <c r="D198" s="11" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="B199" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="C199" s="15"/>
+      <c r="D199" s="13" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="B200" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="C200" s="14"/>
+      <c r="D200" s="11" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="B201" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="C201" s="15"/>
+      <c r="D201" s="13" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="B202" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="C202" s="14"/>
+      <c r="D202" s="11" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="B203" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C203" s="15"/>
+      <c r="D203" s="13" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="B204" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="C204" s="14"/>
+      <c r="D204" s="11" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="B205" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="C205" s="15"/>
+      <c r="D205" s="13" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="B206" s="10" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="8" t="s">
+      <c r="C206" s="14"/>
+      <c r="D206" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="B207" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C207" s="15"/>
+      <c r="D207" s="13" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="B208" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="C208" s="14"/>
+      <c r="D208" s="11" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="B209" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="C209" s="15"/>
+      <c r="D209" s="13" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="B210" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="C210" s="14"/>
+      <c r="D210" s="11" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="B211" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="C211" s="15"/>
+      <c r="D211" s="13" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="B212" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="C212" s="14"/>
+      <c r="D212" s="11" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="B213" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="C213" s="15"/>
+      <c r="D213" s="13" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="B214" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="C214" s="14"/>
+      <c r="D214" s="11" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="B215" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C215" s="15"/>
+      <c r="D215" s="13" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="B216" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="C216" s="14"/>
+      <c r="D216" s="11" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="B217" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="C217" s="15"/>
+      <c r="D217" s="13" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="B218" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="C218" s="14"/>
+      <c r="D218" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="B219" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="B167" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="C167" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="D167" s="11" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="B168" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="C168" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D168" s="9" t="s">
+      <c r="C219" s="15"/>
+      <c r="D219" s="13" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="B220" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="C220" s="14"/>
+      <c r="D220" s="11" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="B221" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="C221" s="15"/>
+      <c r="D221" s="13" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="B222" s="14"/>
+      <c r="C222" s="14"/>
+      <c r="D222" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="B223" s="15"/>
+      <c r="C223" s="15"/>
+      <c r="D223" s="13" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="B224" s="14"/>
+      <c r="C224" s="14"/>
+      <c r="D224" s="16"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="B225" s="15"/>
+      <c r="C225" s="15"/>
+      <c r="D225" s="17"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="B226" s="14"/>
+      <c r="C226" s="14"/>
+      <c r="D226" s="16"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="B227" s="15"/>
+      <c r="C227" s="15"/>
+      <c r="D227" s="17"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="B228" s="14"/>
+      <c r="C228" s="14"/>
+      <c r="D228" s="16"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="B229" s="15"/>
+      <c r="C229" s="15"/>
+      <c r="D229" s="17"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="B230" s="14"/>
+      <c r="C230" s="14"/>
+      <c r="D230" s="16"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="B231" s="15"/>
+      <c r="C231" s="15"/>
+      <c r="D231" s="17"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="B232" s="14"/>
+      <c r="C232" s="14"/>
+      <c r="D232" s="16"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="B233" s="15"/>
+      <c r="C233" s="15"/>
+      <c r="D233" s="17"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B234" s="14"/>
+      <c r="C234" s="14"/>
+      <c r="D234" s="16"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="B235" s="15"/>
+      <c r="C235" s="15"/>
+      <c r="D235" s="17"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="B236" s="14"/>
+      <c r="C236" s="14"/>
+      <c r="D236" s="16"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="B237" s="15"/>
+      <c r="C237" s="15"/>
+      <c r="D237" s="17"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="B238" s="14"/>
+      <c r="C238" s="14"/>
+      <c r="D238" s="16"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="B239" s="15"/>
+      <c r="C239" s="15"/>
+      <c r="D239" s="17"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="B240" s="14"/>
+      <c r="C240" s="14"/>
+      <c r="D240" s="16"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="B241" s="15"/>
+      <c r="C241" s="15"/>
+      <c r="D241" s="17"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="B242" s="14"/>
+      <c r="C242" s="14"/>
+      <c r="D242" s="16"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="B243" s="15"/>
+      <c r="C243" s="15"/>
+      <c r="D243" s="17"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="B244" s="14"/>
+      <c r="C244" s="14"/>
+      <c r="D244" s="16"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="B245" s="15"/>
+      <c r="C245" s="15"/>
+      <c r="D245" s="17"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="B246" s="14"/>
+      <c r="C246" s="14"/>
+      <c r="D246" s="16"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="B247" s="15"/>
+      <c r="C247" s="15"/>
+      <c r="D247" s="17"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="B248" s="14"/>
+      <c r="C248" s="14"/>
+      <c r="D248" s="16"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="B249" s="15"/>
+      <c r="C249" s="15"/>
+      <c r="D249" s="17"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="B250" s="14"/>
+      <c r="C250" s="14"/>
+      <c r="D250" s="16"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="B251" s="15"/>
+      <c r="C251" s="15"/>
+      <c r="D251" s="17"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="B252" s="14"/>
+      <c r="C252" s="14"/>
+      <c r="D252" s="16"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="B253" s="15"/>
+      <c r="C253" s="15"/>
+      <c r="D253" s="17"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="B254" s="14"/>
+      <c r="C254" s="14"/>
+      <c r="D254" s="16"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="B255" s="15"/>
+      <c r="C255" s="15"/>
+      <c r="D255" s="17"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="B256" s="14"/>
+      <c r="C256" s="14"/>
+      <c r="D256" s="16"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="B257" s="15"/>
+      <c r="C257" s="15"/>
+      <c r="D257" s="17"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="B258" s="14"/>
+      <c r="C258" s="14"/>
+      <c r="D258" s="16"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="B259" s="15"/>
+      <c r="C259" s="15"/>
+      <c r="D259" s="17"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="B260" s="14"/>
+      <c r="C260" s="14"/>
+      <c r="D260" s="16"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="B261" s="15"/>
+      <c r="C261" s="15"/>
+      <c r="D261" s="17"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="B262" s="14"/>
+      <c r="C262" s="14"/>
+      <c r="D262" s="16"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="B263" s="15"/>
+      <c r="C263" s="15"/>
+      <c r="D263" s="17"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="B264" s="14"/>
+      <c r="C264" s="14"/>
+      <c r="D264" s="16"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="B265" s="15"/>
+      <c r="C265" s="15"/>
+      <c r="D265" s="17"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="B266" s="14"/>
+      <c r="C266" s="14"/>
+      <c r="D266" s="16"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="B267" s="15"/>
+      <c r="C267" s="15"/>
+      <c r="D267" s="17"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="B268" s="14"/>
+      <c r="C268" s="14"/>
+      <c r="D268" s="16"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="B269" s="15"/>
+      <c r="C269" s="15"/>
+      <c r="D269" s="17"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="B270" s="14"/>
+      <c r="C270" s="14"/>
+      <c r="D270" s="16"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="B271" s="15"/>
+      <c r="C271" s="15"/>
+      <c r="D271" s="17"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="B272" s="14"/>
+      <c r="C272" s="14"/>
+      <c r="D272" s="16"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="B273" s="15"/>
+      <c r="C273" s="15"/>
+      <c r="D273" s="17"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="B274" s="14"/>
+      <c r="C274" s="14"/>
+      <c r="D274" s="16"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="B275" s="15"/>
+      <c r="C275" s="15"/>
+      <c r="D275" s="17"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="B276" s="14"/>
+      <c r="C276" s="14"/>
+      <c r="D276" s="16"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="B277" s="15"/>
+      <c r="C277" s="15"/>
+      <c r="D277" s="17"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="B278" s="14"/>
+      <c r="C278" s="14"/>
+      <c r="D278" s="16"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="B279" s="15"/>
+      <c r="C279" s="15"/>
+      <c r="D279" s="17"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="B280" s="14"/>
+      <c r="C280" s="14"/>
+      <c r="D280" s="16"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="B281" s="15"/>
+      <c r="C281" s="15"/>
+      <c r="D281" s="17"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="B282" s="14"/>
+      <c r="C282" s="14"/>
+      <c r="D282" s="16"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="B283" s="15"/>
+      <c r="C283" s="15"/>
+      <c r="D283" s="17"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="B284" s="14"/>
+      <c r="C284" s="14"/>
+      <c r="D284" s="16"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="B285" s="15"/>
+      <c r="C285" s="15"/>
+      <c r="D285" s="17"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="B286" s="14"/>
+      <c r="C286" s="14"/>
+      <c r="D286" s="16"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="B287" s="15"/>
+      <c r="C287" s="15"/>
+      <c r="D287" s="17"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="B288" s="14"/>
+      <c r="C288" s="14"/>
+      <c r="D288" s="16"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="B289" s="15"/>
+      <c r="C289" s="15"/>
+      <c r="D289" s="17"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="B290" s="14"/>
+      <c r="C290" s="14"/>
+      <c r="D290" s="16"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="B291" s="15"/>
+      <c r="C291" s="15"/>
+      <c r="D291" s="17"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="B292" s="14"/>
+      <c r="C292" s="14"/>
+      <c r="D292" s="16"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="B293" s="15"/>
+      <c r="C293" s="15"/>
+      <c r="D293" s="17"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="B294" s="14"/>
+      <c r="C294" s="14"/>
+      <c r="D294" s="16"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="B295" s="15"/>
+      <c r="C295" s="15"/>
+      <c r="D295" s="17"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="B296" s="14"/>
+      <c r="C296" s="14"/>
+      <c r="D296" s="16"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="B297" s="15"/>
+      <c r="C297" s="15"/>
+      <c r="D297" s="17"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="B298" s="14"/>
+      <c r="C298" s="14"/>
+      <c r="D298" s="16"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="B299" s="15"/>
+      <c r="C299" s="15"/>
+      <c r="D299" s="17"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="B300" s="14"/>
+      <c r="C300" s="14"/>
+      <c r="D300" s="16"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="10" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="B169" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="C169" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="D169" s="11" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="B170" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="C170" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="D170" s="9" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="B171" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="C171" s="10" t="s">
-        <v>312</v>
-      </c>
-      <c r="D171" s="11" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="B172" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="C172" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D172" s="9" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="B173" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="C173" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="D173" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="B174" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="C174" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="D174" s="9" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="B175" s="10" t="s">
-        <v>324</v>
-      </c>
-      <c r="C175" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="D175" s="11" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="B176" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="C176" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="D176" s="9" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="B177" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="C177" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="D177" s="11" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="B178" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="C178" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="D178" s="9" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="B179" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="C179" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="D179" s="11" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="B180" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="C180" s="12"/>
-      <c r="D180" s="9" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="B181" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="C181" s="13"/>
-      <c r="D181" s="11" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="B182" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="C182" s="12"/>
-      <c r="D182" s="9" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="B183" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="C183" s="13"/>
-      <c r="D183" s="11" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="B184" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="C184" s="12"/>
-      <c r="D184" s="9" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="B185" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="C185" s="13"/>
-      <c r="D185" s="11" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="B186" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="C186" s="12"/>
-      <c r="D186" s="9" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="B187" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="C187" s="13"/>
-      <c r="D187" s="11" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="B188" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="C188" s="12"/>
-      <c r="D188" s="9" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="B189" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="C189" s="13"/>
-      <c r="D189" s="11" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="10" t="s">
-        <v>361</v>
-      </c>
-      <c r="B190" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="C190" s="12"/>
-      <c r="D190" s="9" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="B191" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="C191" s="13"/>
-      <c r="D191" s="11" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="B192" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="C192" s="12"/>
-      <c r="D192" s="9" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="B193" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="C193" s="13"/>
-      <c r="D193" s="11" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="B194" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="C194" s="12"/>
-      <c r="D194" s="9" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="B195" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="C195" s="13"/>
-      <c r="D195" s="11" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="B196" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="C196" s="12"/>
-      <c r="D196" s="9" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="B197" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="C197" s="13"/>
-      <c r="D197" s="11" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="B198" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="C198" s="12"/>
-      <c r="D198" s="9" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="B199" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="C199" s="13"/>
-      <c r="D199" s="11" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="B200" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="C200" s="12"/>
-      <c r="D200" s="9" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="B201" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="C201" s="13"/>
-      <c r="D201" s="11" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="B202" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="C202" s="12"/>
-      <c r="D202" s="9" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="B203" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="C203" s="13"/>
-      <c r="D203" s="11" t="s">
+      <c r="B301" s="15"/>
+      <c r="C301" s="15"/>
+      <c r="D301" s="17"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="B302" s="14"/>
+      <c r="C302" s="14"/>
+      <c r="D302" s="16"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="B303" s="15"/>
+      <c r="C303" s="15"/>
+      <c r="D303" s="17"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="B304" s="14"/>
+      <c r="C304" s="14"/>
+      <c r="D304" s="16"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="B305" s="15"/>
+      <c r="C305" s="15"/>
+      <c r="D305" s="17"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="B306" s="14"/>
+      <c r="C306" s="14"/>
+      <c r="D306" s="16"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="B307" s="15"/>
+      <c r="C307" s="15"/>
+      <c r="D307" s="17"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="B308" s="14"/>
+      <c r="C308" s="14"/>
+      <c r="D308" s="16"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="B309" s="15"/>
+      <c r="C309" s="15"/>
+      <c r="D309" s="17"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="B310" s="14"/>
+      <c r="C310" s="14"/>
+      <c r="D310" s="16"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="B311" s="15"/>
+      <c r="C311" s="15"/>
+      <c r="D311" s="17"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="B312" s="14"/>
+      <c r="C312" s="14"/>
+      <c r="D312" s="16"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="B313" s="15"/>
+      <c r="C313" s="15"/>
+      <c r="D313" s="17"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="12" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="10" t="s">
-        <v>384</v>
-      </c>
-      <c r="B204" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="C204" s="12"/>
-      <c r="D204" s="9" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="8" t="s">
-        <v>385</v>
-      </c>
-      <c r="B205" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="C205" s="13"/>
-      <c r="D205" s="11" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="10" t="s">
-        <v>387</v>
-      </c>
-      <c r="B206" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="C206" s="12"/>
-      <c r="D206" s="9" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="B207" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="C207" s="13"/>
-      <c r="D207" s="11" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="B208" s="8" t="s">
-        <v>392</v>
-      </c>
-      <c r="C208" s="12"/>
-      <c r="D208" s="9" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="B209" s="10" t="s">
-        <v>392</v>
-      </c>
-      <c r="C209" s="13"/>
-      <c r="D209" s="11" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="B210" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="C210" s="12"/>
-      <c r="D210" s="9" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="B211" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="C211" s="13"/>
-      <c r="D211" s="11" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="B212" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="C212" s="12"/>
-      <c r="D212" s="9" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="B213" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="C213" s="13"/>
-      <c r="D213" s="11" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="B214" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="C214" s="12"/>
-      <c r="D214" s="9" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="8" t="s">
-        <v>405</v>
-      </c>
-      <c r="B215" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="C215" s="13"/>
-      <c r="D215" s="11" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="B216" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="C216" s="12"/>
-      <c r="D216" s="9" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="B217" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="C217" s="13"/>
-      <c r="D217" s="11" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="B218" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="C218" s="12"/>
-      <c r="D218" s="9" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="B219" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="C219" s="13"/>
-      <c r="D219" s="11" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="B220" s="12"/>
-      <c r="C220" s="12"/>
-      <c r="D220" s="9" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="B221" s="13"/>
-      <c r="C221" s="13"/>
-      <c r="D221" s="11" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="B222" s="12"/>
-      <c r="C222" s="12"/>
-      <c r="D222" s="14"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="8" t="s">
-        <v>414</v>
-      </c>
-      <c r="B223" s="13"/>
-      <c r="C223" s="13"/>
-      <c r="D223" s="15"/>
-    </row>
-    <row r="224">
-      <c r="A224" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="B224" s="12"/>
-      <c r="C224" s="12"/>
-      <c r="D224" s="14"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="B225" s="13"/>
-      <c r="C225" s="13"/>
-      <c r="D225" s="15"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="B226" s="12"/>
-      <c r="C226" s="12"/>
-      <c r="D226" s="14"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="B227" s="13"/>
-      <c r="C227" s="13"/>
-      <c r="D227" s="15"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="10" t="s">
-        <v>416</v>
-      </c>
-      <c r="B228" s="12"/>
-      <c r="C228" s="12"/>
-      <c r="D228" s="14"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="8" t="s">
-        <v>417</v>
-      </c>
-      <c r="B229" s="13"/>
-      <c r="C229" s="13"/>
-      <c r="D229" s="15"/>
-    </row>
-    <row r="230">
-      <c r="A230" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="B230" s="12"/>
-      <c r="C230" s="12"/>
-      <c r="D230" s="14"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="B231" s="13"/>
-      <c r="C231" s="13"/>
-      <c r="D231" s="15"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="10" t="s">
-        <v>419</v>
-      </c>
-      <c r="B232" s="12"/>
-      <c r="C232" s="12"/>
-      <c r="D232" s="14"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="B233" s="13"/>
-      <c r="C233" s="13"/>
-      <c r="D233" s="15"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="B234" s="12"/>
-      <c r="C234" s="12"/>
-      <c r="D234" s="14"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="B235" s="13"/>
-      <c r="C235" s="13"/>
-      <c r="D235" s="15"/>
-    </row>
-    <row r="236">
-      <c r="A236" s="10" t="s">
-        <v>421</v>
-      </c>
-      <c r="B236" s="12"/>
-      <c r="C236" s="12"/>
-      <c r="D236" s="14"/>
-    </row>
-    <row r="237">
-      <c r="A237" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="B237" s="13"/>
-      <c r="C237" s="13"/>
-      <c r="D237" s="15"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="B238" s="12"/>
-      <c r="C238" s="12"/>
-      <c r="D238" s="14"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="8" t="s">
-        <v>423</v>
-      </c>
-      <c r="B239" s="13"/>
-      <c r="C239" s="13"/>
-      <c r="D239" s="15"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="10" t="s">
-        <v>424</v>
-      </c>
-      <c r="B240" s="12"/>
-      <c r="C240" s="12"/>
-      <c r="D240" s="14"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="B241" s="13"/>
-      <c r="C241" s="13"/>
-      <c r="D241" s="15"/>
-    </row>
-    <row r="242">
-      <c r="A242" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="B242" s="12"/>
-      <c r="C242" s="12"/>
-      <c r="D242" s="14"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="8" t="s">
-        <v>425</v>
-      </c>
-      <c r="B243" s="13"/>
-      <c r="C243" s="13"/>
-      <c r="D243" s="15"/>
-    </row>
-    <row r="244">
-      <c r="A244" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="B244" s="12"/>
-      <c r="C244" s="12"/>
-      <c r="D244" s="14"/>
-    </row>
-    <row r="245">
-      <c r="A245" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="B245" s="13"/>
-      <c r="C245" s="13"/>
-      <c r="D245" s="15"/>
-    </row>
-    <row r="246">
-      <c r="A246" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="B246" s="12"/>
-      <c r="C246" s="12"/>
-      <c r="D246" s="14"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="B247" s="13"/>
-      <c r="C247" s="13"/>
-      <c r="D247" s="15"/>
-    </row>
-    <row r="248">
-      <c r="A248" s="10" t="s">
-        <v>427</v>
-      </c>
-      <c r="B248" s="12"/>
-      <c r="C248" s="12"/>
-      <c r="D248" s="14"/>
-    </row>
-    <row r="249">
-      <c r="A249" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="B249" s="13"/>
-      <c r="C249" s="13"/>
-      <c r="D249" s="15"/>
-    </row>
-    <row r="250">
-      <c r="A250" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="B250" s="12"/>
-      <c r="C250" s="12"/>
-      <c r="D250" s="14"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="B251" s="13"/>
-      <c r="C251" s="13"/>
-      <c r="D251" s="15"/>
-    </row>
-    <row r="252">
-      <c r="A252" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="B252" s="12"/>
-      <c r="C252" s="12"/>
-      <c r="D252" s="14"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="B253" s="13"/>
-      <c r="C253" s="13"/>
-      <c r="D253" s="15"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="B254" s="12"/>
-      <c r="C254" s="12"/>
-      <c r="D254" s="14"/>
-    </row>
-    <row r="255">
-      <c r="A255" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="B255" s="13"/>
-      <c r="C255" s="13"/>
-      <c r="D255" s="15"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="10" t="s">
-        <v>431</v>
-      </c>
-      <c r="B256" s="12"/>
-      <c r="C256" s="12"/>
-      <c r="D256" s="14"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="B257" s="13"/>
-      <c r="C257" s="13"/>
-      <c r="D257" s="15"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="B258" s="12"/>
-      <c r="C258" s="12"/>
-      <c r="D258" s="14"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="8" t="s">
+      <c r="B314" s="14"/>
+      <c r="C314" s="14"/>
+      <c r="D314" s="16"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="10" t="s">
         <v>432</v>
       </c>
-      <c r="B259" s="13"/>
-      <c r="C259" s="13"/>
-      <c r="D259" s="15"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="B260" s="12"/>
-      <c r="C260" s="12"/>
-      <c r="D260" s="14"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="B261" s="13"/>
-      <c r="C261" s="13"/>
-      <c r="D261" s="15"/>
-    </row>
-    <row r="262">
-      <c r="A262" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="B262" s="12"/>
-      <c r="C262" s="12"/>
-      <c r="D262" s="14"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="8" t="s">
-        <v>433</v>
-      </c>
-      <c r="B263" s="13"/>
-      <c r="C263" s="13"/>
-      <c r="D263" s="15"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="10" t="s">
-        <v>434</v>
-      </c>
-      <c r="B264" s="12"/>
-      <c r="C264" s="12"/>
-      <c r="D264" s="14"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="B265" s="13"/>
-      <c r="C265" s="13"/>
-      <c r="D265" s="15"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="B266" s="12"/>
-      <c r="C266" s="12"/>
-      <c r="D266" s="14"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="B267" s="13"/>
-      <c r="C267" s="13"/>
-      <c r="D267" s="15"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="10" t="s">
-        <v>435</v>
-      </c>
-      <c r="B268" s="12"/>
-      <c r="C268" s="12"/>
-      <c r="D268" s="14"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="8" t="s">
-        <v>436</v>
-      </c>
-      <c r="B269" s="13"/>
-      <c r="C269" s="13"/>
-      <c r="D269" s="15"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="B270" s="12"/>
-      <c r="C270" s="12"/>
-      <c r="D270" s="14"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="B271" s="13"/>
-      <c r="C271" s="13"/>
-      <c r="D271" s="15"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="10" t="s">
-        <v>438</v>
-      </c>
-      <c r="B272" s="12"/>
-      <c r="C272" s="12"/>
-      <c r="D272" s="14"/>
-    </row>
-    <row r="273">
-      <c r="A273" s="8" t="s">
-        <v>425</v>
-      </c>
-      <c r="B273" s="13"/>
-      <c r="C273" s="13"/>
-      <c r="D273" s="15"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="10" t="s">
-        <v>439</v>
-      </c>
-      <c r="B274" s="12"/>
-      <c r="C274" s="12"/>
-      <c r="D274" s="14"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="8" t="s">
-        <v>419</v>
-      </c>
-      <c r="B275" s="13"/>
-      <c r="C275" s="13"/>
-      <c r="D275" s="15"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="10" t="s">
-        <v>440</v>
-      </c>
-      <c r="B276" s="12"/>
-      <c r="C276" s="12"/>
-      <c r="D276" s="14"/>
-    </row>
-    <row r="277">
-      <c r="A277" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="B277" s="13"/>
-      <c r="C277" s="13"/>
-      <c r="D277" s="15"/>
-    </row>
-    <row r="278">
-      <c r="A278" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="B278" s="12"/>
-      <c r="C278" s="12"/>
-      <c r="D278" s="14"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="8" t="s">
-        <v>391</v>
-      </c>
-      <c r="B279" s="13"/>
-      <c r="C279" s="13"/>
-      <c r="D279" s="15"/>
-    </row>
-    <row r="280">
-      <c r="A280" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="B280" s="12"/>
-      <c r="C280" s="12"/>
-      <c r="D280" s="14"/>
-    </row>
-    <row r="281">
-      <c r="A281" s="8" t="s">
-        <v>441</v>
-      </c>
-      <c r="B281" s="13"/>
-      <c r="C281" s="13"/>
-      <c r="D281" s="15"/>
-    </row>
-    <row r="282">
-      <c r="A282" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="B282" s="12"/>
-      <c r="C282" s="12"/>
-      <c r="D282" s="14"/>
-    </row>
-    <row r="283">
-      <c r="A283" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="B283" s="13"/>
-      <c r="C283" s="13"/>
-      <c r="D283" s="15"/>
-    </row>
-    <row r="284">
-      <c r="A284" s="10" t="s">
-        <v>443</v>
-      </c>
-      <c r="B284" s="12"/>
-      <c r="C284" s="12"/>
-      <c r="D284" s="14"/>
-    </row>
-    <row r="285">
-      <c r="A285" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="B285" s="13"/>
-      <c r="C285" s="13"/>
-      <c r="D285" s="15"/>
-    </row>
-    <row r="286">
-      <c r="A286" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="B286" s="12"/>
-      <c r="C286" s="12"/>
-      <c r="D286" s="14"/>
-    </row>
-    <row r="287">
-      <c r="A287" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="B287" s="13"/>
-      <c r="C287" s="13"/>
-      <c r="D287" s="15"/>
-    </row>
-    <row r="288">
-      <c r="A288" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="B288" s="12"/>
-      <c r="C288" s="12"/>
-      <c r="D288" s="14"/>
-    </row>
-    <row r="289">
-      <c r="A289" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="B289" s="13"/>
-      <c r="C289" s="13"/>
-      <c r="D289" s="15"/>
-    </row>
-    <row r="290">
-      <c r="A290" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="B290" s="12"/>
-      <c r="C290" s="12"/>
-      <c r="D290" s="14"/>
-    </row>
-    <row r="291">
-      <c r="A291" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="B291" s="13"/>
-      <c r="C291" s="13"/>
-      <c r="D291" s="15"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="10" t="s">
-        <v>446</v>
-      </c>
-      <c r="B292" s="12"/>
-      <c r="C292" s="12"/>
-      <c r="D292" s="14"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="B293" s="13"/>
-      <c r="C293" s="13"/>
-      <c r="D293" s="15"/>
-    </row>
-    <row r="294">
-      <c r="A294" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="B294" s="12"/>
-      <c r="C294" s="12"/>
-      <c r="D294" s="14"/>
-    </row>
-    <row r="295">
-      <c r="A295" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="B295" s="13"/>
-      <c r="C295" s="13"/>
-      <c r="D295" s="15"/>
-    </row>
-    <row r="296">
-      <c r="A296" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="B296" s="12"/>
-      <c r="C296" s="12"/>
-      <c r="D296" s="14"/>
-    </row>
-    <row r="297">
-      <c r="A297" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="B297" s="13"/>
-      <c r="C297" s="13"/>
-      <c r="D297" s="15"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="B298" s="12"/>
-      <c r="C298" s="12"/>
-      <c r="D298" s="14"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="B299" s="13"/>
-      <c r="C299" s="13"/>
-      <c r="D299" s="15"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="10" t="s">
-        <v>449</v>
-      </c>
-      <c r="B300" s="12"/>
-      <c r="C300" s="12"/>
-      <c r="D300" s="14"/>
-    </row>
-    <row r="301">
-      <c r="A301" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="B301" s="13"/>
-      <c r="C301" s="13"/>
-      <c r="D301" s="15"/>
-    </row>
-    <row r="302">
-      <c r="A302" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="B302" s="12"/>
-      <c r="C302" s="12"/>
-      <c r="D302" s="14"/>
-    </row>
-    <row r="303">
-      <c r="A303" s="8" t="s">
-        <v>451</v>
-      </c>
-      <c r="B303" s="13"/>
-      <c r="C303" s="13"/>
-      <c r="D303" s="15"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="10" t="s">
-        <v>452</v>
-      </c>
-      <c r="B304" s="12"/>
-      <c r="C304" s="12"/>
-      <c r="D304" s="14"/>
-    </row>
-    <row r="305">
-      <c r="A305" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="B305" s="13"/>
-      <c r="C305" s="13"/>
-      <c r="D305" s="15"/>
-    </row>
-    <row r="306">
-      <c r="A306" s="10" t="s">
-        <v>453</v>
-      </c>
-      <c r="B306" s="12"/>
-      <c r="C306" s="12"/>
-      <c r="D306" s="14"/>
-    </row>
-    <row r="307">
-      <c r="A307" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="B307" s="13"/>
-      <c r="C307" s="13"/>
-      <c r="D307" s="15"/>
-    </row>
-    <row r="308">
-      <c r="A308" s="10" t="s">
-        <v>453</v>
-      </c>
-      <c r="B308" s="12"/>
-      <c r="C308" s="12"/>
-      <c r="D308" s="14"/>
-    </row>
-    <row r="309">
-      <c r="A309" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="B309" s="13"/>
-      <c r="C309" s="13"/>
-      <c r="D309" s="15"/>
-    </row>
-    <row r="310">
-      <c r="A310" s="10" t="s">
-        <v>453</v>
-      </c>
-      <c r="B310" s="12"/>
-      <c r="C310" s="12"/>
-      <c r="D310" s="14"/>
-    </row>
-    <row r="311">
-      <c r="A311" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="B311" s="13"/>
-      <c r="C311" s="13"/>
-      <c r="D311" s="15"/>
-    </row>
-    <row r="312">
-      <c r="A312" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="B312" s="12"/>
-      <c r="C312" s="12"/>
-      <c r="D312" s="14"/>
-    </row>
-    <row r="313">
-      <c r="A313" s="8" t="s">
-        <v>430</v>
-      </c>
-      <c r="B313" s="10" t="s">
-        <v>455</v>
-      </c>
-      <c r="C313" s="13"/>
-      <c r="D313" s="15"/>
-    </row>
-    <row r="314">
-      <c r="A314" s="10" t="s">
-        <v>456</v>
-      </c>
-      <c r="B314" s="12"/>
-      <c r="C314" s="12"/>
-      <c r="D314" s="14"/>
-    </row>
-    <row r="315">
-      <c r="A315" s="8" t="s">
+      <c r="B315" s="12" t="s">
         <v>457</v>
       </c>
-      <c r="B315" s="16"/>
-      <c r="C315" s="16"/>
-      <c r="D315" s="16"/>
+      <c r="C315" s="15"/>
+      <c r="D315" s="17"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="B316" s="14"/>
+      <c r="C316" s="14"/>
+      <c r="D316" s="16"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="B317" s="8"/>
+      <c r="C317" s="8"/>
+      <c r="D317" s="8"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -4905,1342 +4941,1342 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C2" s="4">
         <v>2.9676421809298E13</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="18">
         <v>45923.0</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C3" s="4">
         <v>3.0725212248466E13</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="18">
         <v>45963.0</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C4" s="4">
         <v>3.0365754086162E13</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="18">
         <v>45950.0</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C5" s="4">
         <v>3.3224588062482E13</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="18">
         <v>46063.0</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C6" s="4">
         <v>2.8128124121874E13</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="18">
         <v>45854.0</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
+        <v>476</v>
+      </c>
+      <c r="B7" s="19" t="s">
         <v>474</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>472</v>
-      </c>
-      <c r="C7" s="18">
+      <c r="C7" s="19">
         <v>2.086250911093E13</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="20">
         <v>45524.0</v>
       </c>
-      <c r="E7" s="18" t="s">
-        <v>475</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>476</v>
+      <c r="E7" s="19" t="s">
+        <v>477</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C8" s="4">
         <v>3.1029083512594E13</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="18">
         <v>45974.0</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C9" s="4">
         <v>3.0725249206034E13</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="18">
         <v>45963.0</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C10" s="4">
         <v>3.0411884385938E13</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="18">
         <v>45951.0</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C11" s="4">
         <v>3.395585630389E13</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="18">
         <v>46092.0</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C12" s="4">
         <v>3.3955844058258E13</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="18">
         <v>46092.0</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C13" s="4">
         <v>3.1029096994578E13</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="18">
         <v>45974.0</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C14" s="4">
         <v>2.9771989621778E13</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="18">
         <v>45926.0</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C15" s="4">
         <v>2.5140861016082E13</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="18">
         <v>45722.0</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C16" s="4">
         <v>2.904937130101E13</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="18">
         <v>45905.0</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C17" s="4">
         <v>2.0862509097106E13</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="18">
         <v>45524.0</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C18" s="4">
         <v>2.3503248732818E13</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="18">
         <v>45650.0</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C19" s="4">
         <v>2.9771995259154E13</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="18">
         <v>45926.0</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C20" s="4">
         <v>3.5038938188306E13</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="18">
         <v>46135.0</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C21" s="4">
         <v>3.4125196939154E13</v>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="18">
         <v>46099.0</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C22" s="4">
         <v>3.5039054408082E13</v>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="18">
         <v>46135.0</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C23" s="4">
         <v>3.1028915702546E13</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="18">
         <v>45974.0</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="s">
-        <v>494</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>472</v>
-      </c>
-      <c r="C24" s="18">
+      <c r="A24" s="19" t="s">
+        <v>496</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>474</v>
+      </c>
+      <c r="C24" s="19">
         <v>2.0862509109266E13</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="20">
         <v>45524.0</v>
       </c>
-      <c r="E24" s="18" t="s">
-        <v>475</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>476</v>
+      <c r="E24" s="19" t="s">
+        <v>477</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C25" s="4">
         <v>3.5038775325202E13</v>
       </c>
-      <c r="D25" s="17">
+      <c r="D25" s="18">
         <v>46135.0</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C26" s="4">
         <v>3.503898421173E13</v>
       </c>
-      <c r="D26" s="17">
+      <c r="D26" s="18">
         <v>46135.0</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C27" s="4">
         <v>3.041689677109E13</v>
       </c>
-      <c r="D27" s="17">
+      <c r="D27" s="18">
         <v>45951.0</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C28" s="4">
         <v>2.440784220405E13</v>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="18">
         <v>45692.0</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C29" s="4">
         <v>2.499424266997E13</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="18">
         <v>45716.0</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C30" s="4">
         <v>3.4514436622354E13</v>
       </c>
-      <c r="D30" s="17">
+      <c r="D30" s="18">
         <v>46114.0</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C31" s="4">
         <v>3.0970975231506E13</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="18">
         <v>45972.0</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C32" s="4">
         <v>3.3200330000658E13</v>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="18">
         <v>46062.0</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C33" s="4">
         <v>2.5211065907346E13</v>
       </c>
-      <c r="D33" s="17">
+      <c r="D33" s="18">
         <v>45727.0</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C34" s="4">
         <v>3.3955840192146E13</v>
       </c>
-      <c r="D34" s="17">
+      <c r="D34" s="18">
         <v>46092.0</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C35" s="4">
         <v>2.9772052523154E13</v>
       </c>
-      <c r="D35" s="17">
+      <c r="D35" s="18">
         <v>45926.0</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C36" s="4">
         <v>2.125082728885E13</v>
       </c>
-      <c r="D36" s="17">
+      <c r="D36" s="18">
         <v>46104.0</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C37" s="4">
         <v>3.5038652960402E13</v>
       </c>
-      <c r="D37" s="17">
+      <c r="D37" s="18">
         <v>46135.0</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C38" s="4">
         <v>3.1368685562002E13</v>
       </c>
-      <c r="D38" s="17">
+      <c r="D38" s="18">
         <v>45987.0</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C39" s="4">
         <v>3.5038986006674E13</v>
       </c>
-      <c r="D39" s="17">
+      <c r="D39" s="18">
         <v>46135.0</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C40" s="4">
         <v>2.086251419637E13</v>
       </c>
-      <c r="D40" s="17">
+      <c r="D40" s="18">
         <v>45524.0</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="s">
-        <v>511</v>
-      </c>
-      <c r="B41" s="18" t="s">
-        <v>472</v>
-      </c>
-      <c r="C41" s="18">
+      <c r="A41" s="19" t="s">
+        <v>513</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>474</v>
+      </c>
+      <c r="C41" s="19">
         <v>2.1250680239762E13</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="20">
         <v>46148.0</v>
       </c>
-      <c r="E41" s="18" t="s">
-        <v>466</v>
-      </c>
-      <c r="F41" s="18" t="s">
-        <v>476</v>
+      <c r="E41" s="19" t="s">
+        <v>468</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C42" s="4">
         <v>3.102905894453E13</v>
       </c>
-      <c r="D42" s="17">
+      <c r="D42" s="18">
         <v>45974.0</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C43" s="4">
         <v>3.5038213809426E13</v>
       </c>
-      <c r="D43" s="17">
+      <c r="D43" s="18">
         <v>46135.0</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C44" s="4">
         <v>3.503895689077E13</v>
       </c>
-      <c r="D44" s="17">
+      <c r="D44" s="18">
         <v>46135.0</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C45" s="4">
         <v>2.1250842116626E13</v>
       </c>
-      <c r="D45" s="17">
+      <c r="D45" s="18">
         <v>46141.0</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C46" s="4">
         <v>2.321857987125E13</v>
       </c>
-      <c r="D46" s="17">
+      <c r="D46" s="18">
         <v>45730.0</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C47" s="4">
         <v>2.6367127460498E13</v>
       </c>
-      <c r="D47" s="17">
+      <c r="D47" s="18">
         <v>45776.0</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="s">
-        <v>518</v>
-      </c>
-      <c r="B48" s="18" t="s">
-        <v>472</v>
-      </c>
-      <c r="C48" s="18">
+      <c r="A48" s="19" t="s">
+        <v>520</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>474</v>
+      </c>
+      <c r="C48" s="19">
         <v>2.1201306990354E13</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="20">
         <v>46153.0</v>
       </c>
-      <c r="E48" s="18" t="s">
-        <v>466</v>
-      </c>
-      <c r="F48" s="18" t="s">
-        <v>476</v>
+      <c r="E48" s="19" t="s">
+        <v>468</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C49" s="4">
         <v>3.5018413849362E13</v>
       </c>
-      <c r="D49" s="17">
+      <c r="D49" s="18">
         <v>46134.0</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C50" s="4">
         <v>3.082432269493E13</v>
       </c>
-      <c r="D50" s="17">
+      <c r="D50" s="18">
         <v>45966.0</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C51" s="4">
         <v>3.5039050046866E13</v>
       </c>
-      <c r="D51" s="17">
+      <c r="D51" s="18">
         <v>46135.0</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C52" s="4">
         <v>3.3955841621266E13</v>
       </c>
-      <c r="D52" s="17">
+      <c r="D52" s="18">
         <v>46092.0</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C53" s="4">
         <v>2.2016222537234E13</v>
       </c>
-      <c r="D53" s="17">
+      <c r="D53" s="18">
         <v>45671.0</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C54" s="4">
         <v>3.4541093094802E13</v>
       </c>
-      <c r="D54" s="17">
+      <c r="D54" s="18">
         <v>46115.0</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C55" s="4">
         <v>3.454104964981E13</v>
       </c>
-      <c r="D55" s="17">
+      <c r="D55" s="18">
         <v>46141.0</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C56" s="4">
         <v>2.1250903271954E13</v>
       </c>
-      <c r="D56" s="17">
+      <c r="D56" s="18">
         <v>45544.0</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C57" s="4">
         <v>2.9771972975122E13</v>
       </c>
-      <c r="D57" s="17">
+      <c r="D57" s="18">
         <v>45926.0</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C58" s="4">
         <v>2.0862514183058E13</v>
       </c>
-      <c r="D58" s="17">
+      <c r="D58" s="18">
         <v>45524.0</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C59" s="4">
         <v>3.3955827087122E13</v>
       </c>
-      <c r="D59" s="17">
+      <c r="D59" s="18">
         <v>46092.0</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C60" s="4">
         <v>3.102912725365E13</v>
       </c>
-      <c r="D60" s="17">
+      <c r="D60" s="18">
         <v>45974.0</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C61" s="4">
         <v>2.1250939822354E13</v>
       </c>
-      <c r="D61" s="17">
+      <c r="D61" s="18">
         <v>45544.0</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="s">
-        <v>532</v>
-      </c>
-      <c r="B62" s="18" t="s">
-        <v>472</v>
-      </c>
-      <c r="C62" s="18">
+      <c r="A62" s="19" t="s">
+        <v>534</v>
+      </c>
+      <c r="B62" s="19" t="s">
+        <v>474</v>
+      </c>
+      <c r="C62" s="19">
         <v>2.0862514191506E13</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="20">
         <v>45524.0</v>
       </c>
-      <c r="E62" s="18" t="s">
-        <v>475</v>
-      </c>
-      <c r="F62" s="18" t="s">
-        <v>476</v>
+      <c r="E62" s="19" t="s">
+        <v>477</v>
+      </c>
+      <c r="F62" s="19" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C63" s="4">
         <v>2.7433474056978E13</v>
       </c>
-      <c r="D63" s="17">
+      <c r="D63" s="18">
         <v>45824.0</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C64" s="4">
         <v>3.445617546613E13</v>
       </c>
-      <c r="D64" s="17">
+      <c r="D64" s="18">
         <v>46112.0</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C65" s="4">
         <v>3.445631659509E13</v>
       </c>
-      <c r="D65" s="17">
+      <c r="D65" s="18">
         <v>46112.0</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C66" s="4">
         <v>2.086254321461E13</v>
       </c>
-      <c r="D66" s="17">
+      <c r="D66" s="18">
         <v>45524.0</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C67" s="4">
         <v>2.7433474056338E13</v>
       </c>
-      <c r="D67" s="17">
+      <c r="D67" s="18">
         <v>45824.0</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="68">
@@ -6248,159 +6284,159 @@
         <v>2</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C68" s="4">
         <v>3.503887818933E13</v>
       </c>
-      <c r="D68" s="17">
+      <c r="D68" s="18">
         <v>46135.0</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C69" s="4">
         <v>3.041182882037E13</v>
       </c>
-      <c r="D69" s="17">
+      <c r="D69" s="18">
         <v>45951.0</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C70" s="4">
         <v>2.0862514193426E13</v>
       </c>
-      <c r="D70" s="17">
+      <c r="D70" s="18">
         <v>45524.0</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C71" s="4">
         <v>3.0416876887826E13</v>
       </c>
-      <c r="D71" s="17">
+      <c r="D71" s="18">
         <v>45951.0</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C72" s="4">
         <v>3.0416887609234E13</v>
       </c>
-      <c r="D72" s="17">
+      <c r="D72" s="18">
         <v>45951.0</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C73" s="4">
         <v>3.3249444208786E13</v>
       </c>
-      <c r="D73" s="17">
+      <c r="D73" s="18">
         <v>46097.0</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C74" s="4">
         <v>2.1250891277458E13</v>
       </c>
-      <c r="D74" s="17">
+      <c r="D74" s="18">
         <v>45544.0</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C75" s="4">
         <v>3.1368973395474E13</v>
       </c>
-      <c r="D75" s="17">
+      <c r="D75" s="18">
         <v>45987.0</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -6423,86 +6459,86 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="s">
-        <v>546</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>547</v>
-      </c>
-      <c r="C1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>548</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="B1" s="21" t="s">
         <v>549</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="C1" s="21" t="s">
         <v>550</v>
       </c>
+      <c r="D1" s="21" t="s">
+        <v>551</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>552</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="s">
-        <v>551</v>
-      </c>
-      <c r="B2" s="22">
+      <c r="A2" s="22" t="s">
+        <v>553</v>
+      </c>
+      <c r="B2" s="23">
         <v>46155.782638888886</v>
       </c>
-      <c r="C2" s="23" t="s">
-        <v>552</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>553</v>
-      </c>
-      <c r="E2" s="23" t="s">
+      <c r="C2" s="24" t="s">
         <v>554</v>
       </c>
+      <c r="D2" s="24" t="s">
+        <v>555</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>556</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="s">
-        <v>555</v>
-      </c>
-      <c r="B3" s="22">
+      <c r="A3" s="25" t="s">
+        <v>557</v>
+      </c>
+      <c r="B3" s="23">
         <v>46155.78472222222</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="25" t="s">
+        <v>558</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>559</v>
+      </c>
+      <c r="E3" s="25" t="s">
         <v>556</v>
       </c>
-      <c r="D3" s="24" t="s">
-        <v>557</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>554</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="s">
-        <v>558</v>
-      </c>
-      <c r="B4" s="25">
+      <c r="A4" s="25" t="s">
+        <v>560</v>
+      </c>
+      <c r="B4" s="26">
         <v>46148.686111111114</v>
       </c>
-      <c r="C4" s="24" t="s">
-        <v>559</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>560</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>554</v>
+      <c r="C4" s="25" t="s">
+        <v>561</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>562</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
+      <c r="A5" s="27"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
     </row>
     <row r="6">
-      <c r="A6" s="26"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
     </row>
   </sheetData>
   <printOptions/>
